--- a/Conversation_List/Conversation_List_Test_Cases.xlsx
+++ b/Conversation_List/Conversation_List_Test_Cases.xlsx
@@ -2,8 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Conversation List Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Functional" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Integration" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Regression" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Security" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Edge Cases" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Boundary Values" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Equivalence Partitioning" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13,90 +23,41 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color theme="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color theme="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font/>
   </fonts>
   <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
-    <border/>
+  <borders count="2">
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
@@ -108,37 +69,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -211,20 +154,20 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="4F81BD"/>
@@ -248,19 +191,77 @@
         <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -272,159 +273,190 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.29" customWidth="1" style="7" min="1" max="1"/>
-    <col width="10" customWidth="1" style="7" min="2" max="2"/>
-    <col width="26" customWidth="1" style="7" min="3" max="3"/>
-    <col width="32" customWidth="1" style="7" min="4" max="4"/>
-    <col width="34" customWidth="1" style="7" min="5" max="5"/>
-    <col width="38" customWidth="1" style="7" min="6" max="6"/>
-    <col width="44" customWidth="1" style="7" min="7" max="7"/>
-    <col width="18" customWidth="1" style="7" min="8" max="8"/>
-    <col width="8.710000000000001" customWidth="1" style="7" min="9" max="26"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="7">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
@@ -472,7 +504,7 @@
           <t>CL_001</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -515,9 +547,9 @@
           <t>CL_002</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify user conversation displays name and avatar</t>
@@ -545,9 +577,9 @@
           <t>CL_003</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify group conversation displays name and avatar</t>
@@ -575,9 +607,9 @@
           <t>CL_004</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n"/>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify online status indicator</t>
@@ -605,9 +637,9 @@
           <t>CL_005</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n"/>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify conversations sorted by recent activity</t>
@@ -636,9 +668,9 @@
           <t>CL_006</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n"/>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="10" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify clicking conversation opens chat</t>
@@ -709,7 +741,7 @@
           <t>CL_008</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -751,9 +783,9 @@
           <t>CL_009</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="10" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Verify delete confirmation dialog</t>
@@ -781,8 +813,8 @@
           <t>CL_010</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t>User is logged in and delete dialog shown</t>
@@ -815,9 +847,9 @@
           <t>CL_011</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Verify cancel delete keeps conversation</t>
@@ -888,7 +920,7 @@
           <t>CL_013</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -930,9 +962,9 @@
           <t>CL_014</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Verify yesterday's conversation shows 'Yesterday'</t>
@@ -960,9 +992,9 @@
           <t>CL_015</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Verify older conversation shows date</t>
@@ -990,9 +1022,9 @@
           <t>CL_016</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Verify date updates after midnight</t>
@@ -1021,7 +1053,7 @@
           <t>CL_017</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1063,9 +1095,9 @@
           <t>CL_018</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Verify 'You:' prefix for sent messages</t>
@@ -1094,9 +1126,9 @@
           <t>CL_019</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Verify message status checkmark</t>
@@ -1118,15 +1150,15 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="7">
+    <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>CL_020</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Verify long message truncation</t>
@@ -1149,15 +1181,15 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" s="7">
+    <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>CL_021</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Verify image/attachment preview</t>
@@ -1180,15 +1212,15 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="7">
+    <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>CL_022</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Verify preview updates on new message</t>
@@ -1211,7 +1243,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="7">
+    <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>CL_023</t>
@@ -1253,7 +1285,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1" s="7">
+    <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>CL_024</t>
@@ -1296,1909 +1328,1347 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1" s="7">
-      <c r="A26" s="11" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CL_025</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Integration: Conversation List with Message List</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in with conversations</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify opening conversation navigates to correct message list</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Click on a conversation.
 2. Verify messages belong to that conversation.</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Message list should load messages only for the selected conversation. No cross-conversation data.</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1" s="7">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CL_026</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr"/>
-      <c r="C27" s="11" t="inlineStr"/>
-      <c r="D27" s="11" t="inlineStr"/>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify new message updates conversation list preview and order</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Send a message in an older conversation.
 2. Observe conversation list.</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Conversation should move to top with updated preview message and timestamp.</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1" s="7">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CL_027</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr"/>
-      <c r="C28" s="11" t="inlineStr"/>
-      <c r="D28" s="11" t="inlineStr"/>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify read status syncs between conversation list and message list</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Open an unread conversation.
 2. Read messages.
 3. Go back to list.</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Unread badge should disappear from the conversation in the list.</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1" s="7">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>CL_028</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr"/>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Integration: Conversation List with Notifications</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>User is logged in, app in background</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify notification updates conversation list on app resume</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Receive messages while app is in background.
 2. Open app.</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Conversation list should refresh with new messages reflected in preview and order.</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" s="7">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFC000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CL_029</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Regression: Conversation List after actions</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in with conversations</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify conversation list intact after deleting a conversation</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Delete a conversation.
 2. Observe remaining conversations.</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Remaining conversations should maintain correct order, previews, and timestamps. No data corruption.</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1" s="7">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CL_030</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr"/>
-      <c r="C31" s="11" t="inlineStr"/>
-      <c r="D31" s="11" t="inlineStr"/>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify conversation list intact after blocking a user</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Block a user.
 2. Observe conversation list.</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Blocked user's conversation should be handled per app policy (hidden or marked). Other conversations unaffected.</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1" s="7">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CL_031</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr"/>
-      <c r="C32" s="11" t="inlineStr"/>
-      <c r="D32" s="11" t="inlineStr"/>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify conversation list after app update/restart</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Close and reopen the app.
 2. Observe conversation list.</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>All conversations should reload correctly with accurate previews and order.</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1" s="7">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>CL_032</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr"/>
-      <c r="C33" s="11" t="inlineStr"/>
-      <c r="D33" s="11" t="inlineStr"/>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify conversation list after logout and re-login</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Logout.
 2. Login with same account.
 3. Observe conversation list.</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>All previous conversations should load correctly.</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1" s="7">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FF0000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CL_033</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Security: Conversation List</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify conversation list shows only authorized conversations</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Login as User A.
 2. Observe conversation list.</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Only conversations where User A is a participant should display. No other users' conversations visible.</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1" s="7">
-      <c r="A35" s="11" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CL_034</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr"/>
-      <c r="C35" s="11" t="inlineStr"/>
-      <c r="D35" s="11" t="inlineStr"/>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify conversation preview does not expose sensitive data</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Observe preview messages in conversation list.</t>
         </is>
       </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Sensitive content (passwords, tokens) should not be visible in preview. Media messages should show placeholder text.</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1" s="7">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CL_035</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Security: Conversation List</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>User is not logged in</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify conversation list not accessible without authentication</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Try to access conversation list without logging in.</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Should redirect to login page. No conversation data should be exposed.</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1" s="7">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>CL_036</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr"/>
-      <c r="C37" s="11" t="inlineStr"/>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>User session expired</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify conversation list handles expired session</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Let session expire.
 2. Try to interact with conversation list.</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Should prompt re-authentication. No stale data should be accessible.</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1" s="7">
-      <c r="A38" s="11" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CL_037</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Edge Case: Conversation List</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify conversation list with 1000+ conversations</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Have an account with 1000+ conversations.
 2. Open conversation list.</t>
         </is>
       </c>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>List should load with pagination/infinite scroll. No performance degradation or crash.</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1" s="7">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CL_038</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr"/>
-      <c r="C39" s="11" t="inlineStr"/>
-      <c r="D39" s="11" t="inlineStr"/>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify conversation with extremely long group name</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Create a group with a 255-character name.
 2. Observe in conversation list.</t>
         </is>
       </c>
-      <c r="G39" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Group name should truncate with ellipsis. No layout breaking.</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1" s="7">
-      <c r="A40" s="11" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CL_039</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr"/>
-      <c r="C40" s="11" t="inlineStr"/>
-      <c r="D40" s="11" t="inlineStr"/>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify conversation with special characters in name</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Have a conversation with user/group name containing emojis, unicode, RTL characters.</t>
         </is>
       </c>
-      <c r="G40" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Name should display correctly without rendering issues.</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1" s="7">
-      <c r="A41" s="11" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>CL_040</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr"/>
-      <c r="C41" s="11" t="inlineStr"/>
-      <c r="D41" s="11" t="inlineStr"/>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify conversation list with rapid message updates</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Receive 50+ messages in quick succession across different conversations.</t>
         </is>
       </c>
-      <c r="G41" s="11" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>List should update smoothly without flickering, freezing, or incorrect ordering.</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1" s="7">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>CL_041</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr"/>
-      <c r="C42" s="11" t="inlineStr"/>
-      <c r="D42" s="11" t="inlineStr"/>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify conversation preview with empty message (media only)</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. Send an image with no caption in a conversation.
 2. Observe preview.</t>
         </is>
       </c>
-      <c r="G42" s="11" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Preview should show placeholder like '📷 Photo' or 'Image' instead of blank.</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1" s="7">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>CL_042</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Edge Case: Conversation List</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify conversation list when server returns error</t>
         </is>
       </c>
-      <c r="F43" s="11" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Simulate server error (500).
 2. Observe conversation list.</t>
         </is>
       </c>
-      <c r="G43" s="11" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Error message should display with retry option. App should not crash.</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1" s="7">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>CL_043</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr"/>
-      <c r="C44" s="11" t="inlineStr"/>
-      <c r="D44" s="11" t="inlineStr"/>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Verify conversation list with slow network (2G/3G)</t>
         </is>
       </c>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Throttle network to 2G speed.
 2. Open conversation list.</t>
         </is>
       </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Loading indicator should show. List should eventually load. No timeout crash.</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1" s="7">
-      <c r="A45" s="11" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CL_044</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Boundary: Conversation List</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify conversation list with exactly 0 conversations</t>
         </is>
       </c>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Login with new account with no conversations.</t>
         </is>
       </c>
-      <c r="G45" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Empty state should display correctly with appropriate message.</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1" s="7">
-      <c r="A46" s="11" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CL_045</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr"/>
-      <c r="C46" s="11" t="inlineStr"/>
-      <c r="D46" s="11" t="inlineStr"/>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify conversation list with exactly 1 conversation</t>
         </is>
       </c>
-      <c r="F46" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Have exactly 1 conversation.
 2. Open list.</t>
         </is>
       </c>
-      <c r="G46" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Single conversation should display correctly with all elements.</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1" s="7">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CL_046</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr"/>
-      <c r="C47" s="11" t="inlineStr"/>
-      <c r="D47" s="11" t="inlineStr"/>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify preview message with 1 character</t>
         </is>
       </c>
-      <c r="F47" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Send a single character message.
 2. Observe preview.</t>
         </is>
       </c>
-      <c r="G47" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Single character should display correctly in preview.</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1" s="7">
-      <c r="A48" s="11" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>CL_047</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr"/>
-      <c r="C48" s="11" t="inlineStr"/>
-      <c r="D48" s="11" t="inlineStr"/>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify preview message with maximum length text</t>
         </is>
       </c>
-      <c r="F48" s="11" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Send a very long message (5000+ chars).
 2. Observe preview.</t>
         </is>
       </c>
-      <c r="G48" s="11" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Preview should truncate appropriately with ellipsis.</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1" s="7">
-      <c r="A49" s="11" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B0F0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CL_048</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Conversation Types</t>
         </is>
       </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify one-on-one conversation display</t>
         </is>
       </c>
-      <c r="F49" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Observe a one-on-one conversation in list.</t>
         </is>
       </c>
-      <c r="G49" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Should show user avatar, name, last message preview, time, and unread count.</t>
         </is>
       </c>
-      <c r="H49" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1" s="7">
-      <c r="A50" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CL_049</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr"/>
-      <c r="C50" s="11" t="inlineStr"/>
-      <c r="D50" s="11" t="inlineStr"/>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify public group conversation display</t>
         </is>
       </c>
-      <c r="F50" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Observe a public group conversation in list.</t>
         </is>
       </c>
-      <c r="G50" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Should show group avatar, group name, last message with sender prefix, time.</t>
         </is>
       </c>
-      <c r="H50" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1" s="7">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CL_050</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr"/>
-      <c r="C51" s="11" t="inlineStr"/>
-      <c r="D51" s="11" t="inlineStr"/>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify private group conversation display</t>
         </is>
       </c>
-      <c r="F51" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Observe a private group conversation in list.</t>
         </is>
       </c>
-      <c r="G51" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Should show group avatar with lock icon, group name, last message, time.</t>
         </is>
       </c>
-      <c r="H51" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1" s="7">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>CL_051</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr"/>
-      <c r="C52" s="11" t="inlineStr"/>
-      <c r="D52" s="11" t="inlineStr"/>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify password-protected group conversation display</t>
         </is>
       </c>
-      <c r="F52" s="11" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Observe a password-protected group conversation in list.</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Should show group avatar, group name, last message, time. Password icon if applicable.</t>
         </is>
       </c>
-      <c r="H52" s="11" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1" s="7"/>
-    <row r="54" ht="15.75" customHeight="1" s="7"/>
-    <row r="55" ht="15.75" customHeight="1" s="7"/>
-    <row r="56" ht="15.75" customHeight="1" s="7"/>
-    <row r="57" ht="15.75" customHeight="1" s="7"/>
-    <row r="58" ht="15.75" customHeight="1" s="7"/>
-    <row r="59" ht="15.75" customHeight="1" s="7"/>
-    <row r="60" ht="15.75" customHeight="1" s="7"/>
-    <row r="61" ht="15.75" customHeight="1" s="7"/>
-    <row r="62" ht="15.75" customHeight="1" s="7"/>
-    <row r="63" ht="15.75" customHeight="1" s="7"/>
-    <row r="64" ht="15.75" customHeight="1" s="7"/>
-    <row r="65" ht="15.75" customHeight="1" s="7"/>
-    <row r="66" ht="15.75" customHeight="1" s="7"/>
-    <row r="67" ht="15.75" customHeight="1" s="7"/>
-    <row r="68" ht="15.75" customHeight="1" s="7"/>
-    <row r="69" ht="15.75" customHeight="1" s="7"/>
-    <row r="70" ht="15.75" customHeight="1" s="7"/>
-    <row r="71" ht="15.75" customHeight="1" s="7"/>
-    <row r="72" ht="15.75" customHeight="1" s="7"/>
-    <row r="73" ht="15.75" customHeight="1" s="7"/>
-    <row r="74" ht="15.75" customHeight="1" s="7"/>
-    <row r="75" ht="15.75" customHeight="1" s="7"/>
-    <row r="76" ht="15.75" customHeight="1" s="7"/>
-    <row r="77" ht="15.75" customHeight="1" s="7"/>
-    <row r="78" ht="15.75" customHeight="1" s="7"/>
-    <row r="79" ht="15.75" customHeight="1" s="7"/>
-    <row r="80" ht="15.75" customHeight="1" s="7"/>
-    <row r="81" ht="15.75" customHeight="1" s="7"/>
-    <row r="82" ht="15.75" customHeight="1" s="7"/>
-    <row r="83" ht="15.75" customHeight="1" s="7"/>
-    <row r="84" ht="15.75" customHeight="1" s="7"/>
-    <row r="85" ht="15.75" customHeight="1" s="7"/>
-    <row r="86" ht="15.75" customHeight="1" s="7"/>
-    <row r="87" ht="15.75" customHeight="1" s="7"/>
-    <row r="88" ht="15.75" customHeight="1" s="7"/>
-    <row r="89" ht="15.75" customHeight="1" s="7"/>
-    <row r="90" ht="15.75" customHeight="1" s="7"/>
-    <row r="91" ht="15.75" customHeight="1" s="7"/>
-    <row r="92" ht="15.75" customHeight="1" s="7"/>
-    <row r="93" ht="15.75" customHeight="1" s="7"/>
-    <row r="94" ht="15.75" customHeight="1" s="7"/>
-    <row r="95" ht="15.75" customHeight="1" s="7"/>
-    <row r="96" ht="15.75" customHeight="1" s="7"/>
-    <row r="97" ht="15.75" customHeight="1" s="7"/>
-    <row r="98" ht="15.75" customHeight="1" s="7"/>
-    <row r="99" ht="15.75" customHeight="1" s="7"/>
-    <row r="100" ht="15.75" customHeight="1" s="7"/>
-    <row r="101" ht="15.75" customHeight="1" s="7"/>
-    <row r="102" ht="15.75" customHeight="1" s="7"/>
-    <row r="103" ht="15.75" customHeight="1" s="7"/>
-    <row r="104" ht="15.75" customHeight="1" s="7"/>
-    <row r="105" ht="15.75" customHeight="1" s="7"/>
-    <row r="106" ht="15.75" customHeight="1" s="7"/>
-    <row r="107" ht="15.75" customHeight="1" s="7"/>
-    <row r="108" ht="15.75" customHeight="1" s="7"/>
-    <row r="109" ht="15.75" customHeight="1" s="7"/>
-    <row r="110" ht="15.75" customHeight="1" s="7"/>
-    <row r="111" ht="15.75" customHeight="1" s="7"/>
-    <row r="112" ht="15.75" customHeight="1" s="7"/>
-    <row r="113" ht="15.75" customHeight="1" s="7"/>
-    <row r="114" ht="15.75" customHeight="1" s="7"/>
-    <row r="115" ht="15.75" customHeight="1" s="7"/>
-    <row r="116" ht="15.75" customHeight="1" s="7"/>
-    <row r="117" ht="15.75" customHeight="1" s="7"/>
-    <row r="118" ht="15.75" customHeight="1" s="7"/>
-    <row r="119" ht="15.75" customHeight="1" s="7"/>
-    <row r="120" ht="15.75" customHeight="1" s="7"/>
-    <row r="121" ht="15.75" customHeight="1" s="7"/>
-    <row r="122" ht="15.75" customHeight="1" s="7"/>
-    <row r="123" ht="15.75" customHeight="1" s="7"/>
-    <row r="124" ht="15.75" customHeight="1" s="7"/>
-    <row r="125" ht="15.75" customHeight="1" s="7"/>
-    <row r="126" ht="15.75" customHeight="1" s="7"/>
-    <row r="127" ht="15.75" customHeight="1" s="7"/>
-    <row r="128" ht="15.75" customHeight="1" s="7"/>
-    <row r="129" ht="15.75" customHeight="1" s="7"/>
-    <row r="130" ht="15.75" customHeight="1" s="7"/>
-    <row r="131" ht="15.75" customHeight="1" s="7"/>
-    <row r="132" ht="15.75" customHeight="1" s="7"/>
-    <row r="133" ht="15.75" customHeight="1" s="7"/>
-    <row r="134" ht="15.75" customHeight="1" s="7"/>
-    <row r="135" ht="15.75" customHeight="1" s="7"/>
-    <row r="136" ht="15.75" customHeight="1" s="7"/>
-    <row r="137" ht="15.75" customHeight="1" s="7"/>
-    <row r="138" ht="15.75" customHeight="1" s="7"/>
-    <row r="139" ht="15.75" customHeight="1" s="7"/>
-    <row r="140" ht="15.75" customHeight="1" s="7"/>
-    <row r="141" ht="15.75" customHeight="1" s="7"/>
-    <row r="142" ht="15.75" customHeight="1" s="7"/>
-    <row r="143" ht="15.75" customHeight="1" s="7"/>
-    <row r="144" ht="15.75" customHeight="1" s="7"/>
-    <row r="145" ht="15.75" customHeight="1" s="7"/>
-    <row r="146" ht="15.75" customHeight="1" s="7"/>
-    <row r="147" ht="15.75" customHeight="1" s="7"/>
-    <row r="148" ht="15.75" customHeight="1" s="7"/>
-    <row r="149" ht="15.75" customHeight="1" s="7"/>
-    <row r="150" ht="15.75" customHeight="1" s="7"/>
-    <row r="151" ht="15.75" customHeight="1" s="7"/>
-    <row r="152" ht="15.75" customHeight="1" s="7"/>
-    <row r="153" ht="15.75" customHeight="1" s="7"/>
-    <row r="154" ht="15.75" customHeight="1" s="7"/>
-    <row r="155" ht="15.75" customHeight="1" s="7"/>
-    <row r="156" ht="15.75" customHeight="1" s="7"/>
-    <row r="157" ht="15.75" customHeight="1" s="7"/>
-    <row r="158" ht="15.75" customHeight="1" s="7"/>
-    <row r="159" ht="15.75" customHeight="1" s="7"/>
-    <row r="160" ht="15.75" customHeight="1" s="7"/>
-    <row r="161" ht="15.75" customHeight="1" s="7"/>
-    <row r="162" ht="15.75" customHeight="1" s="7"/>
-    <row r="163" ht="15.75" customHeight="1" s="7"/>
-    <row r="164" ht="15.75" customHeight="1" s="7"/>
-    <row r="165" ht="15.75" customHeight="1" s="7"/>
-    <row r="166" ht="15.75" customHeight="1" s="7"/>
-    <row r="167" ht="15.75" customHeight="1" s="7"/>
-    <row r="168" ht="15.75" customHeight="1" s="7"/>
-    <row r="169" ht="15.75" customHeight="1" s="7"/>
-    <row r="170" ht="15.75" customHeight="1" s="7"/>
-    <row r="171" ht="15.75" customHeight="1" s="7"/>
-    <row r="172" ht="15.75" customHeight="1" s="7"/>
-    <row r="173" ht="15.75" customHeight="1" s="7"/>
-    <row r="174" ht="15.75" customHeight="1" s="7"/>
-    <row r="175" ht="15.75" customHeight="1" s="7"/>
-    <row r="176" ht="15.75" customHeight="1" s="7"/>
-    <row r="177" ht="15.75" customHeight="1" s="7"/>
-    <row r="178" ht="15.75" customHeight="1" s="7"/>
-    <row r="179" ht="15.75" customHeight="1" s="7"/>
-    <row r="180" ht="15.75" customHeight="1" s="7"/>
-    <row r="181" ht="15.75" customHeight="1" s="7"/>
-    <row r="182" ht="15.75" customHeight="1" s="7"/>
-    <row r="183" ht="15.75" customHeight="1" s="7"/>
-    <row r="184" ht="15.75" customHeight="1" s="7"/>
-    <row r="185" ht="15.75" customHeight="1" s="7"/>
-    <row r="186" ht="15.75" customHeight="1" s="7"/>
-    <row r="187" ht="15.75" customHeight="1" s="7"/>
-    <row r="188" ht="15.75" customHeight="1" s="7"/>
-    <row r="189" ht="15.75" customHeight="1" s="7"/>
-    <row r="190" ht="15.75" customHeight="1" s="7"/>
-    <row r="191" ht="15.75" customHeight="1" s="7"/>
-    <row r="192" ht="15.75" customHeight="1" s="7"/>
-    <row r="193" ht="15.75" customHeight="1" s="7"/>
-    <row r="194" ht="15.75" customHeight="1" s="7"/>
-    <row r="195" ht="15.75" customHeight="1" s="7"/>
-    <row r="196" ht="15.75" customHeight="1" s="7"/>
-    <row r="197" ht="15.75" customHeight="1" s="7"/>
-    <row r="198" ht="15.75" customHeight="1" s="7"/>
-    <row r="199" ht="15.75" customHeight="1" s="7"/>
-    <row r="200" ht="15.75" customHeight="1" s="7"/>
-    <row r="201" ht="15.75" customHeight="1" s="7"/>
-    <row r="202" ht="15.75" customHeight="1" s="7"/>
-    <row r="203" ht="15.75" customHeight="1" s="7"/>
-    <row r="204" ht="15.75" customHeight="1" s="7"/>
-    <row r="205" ht="15.75" customHeight="1" s="7"/>
-    <row r="206" ht="15.75" customHeight="1" s="7"/>
-    <row r="207" ht="15.75" customHeight="1" s="7"/>
-    <row r="208" ht="15.75" customHeight="1" s="7"/>
-    <row r="209" ht="15.75" customHeight="1" s="7"/>
-    <row r="210" ht="15.75" customHeight="1" s="7"/>
-    <row r="211" ht="15.75" customHeight="1" s="7"/>
-    <row r="212" ht="15.75" customHeight="1" s="7"/>
-    <row r="213" ht="15.75" customHeight="1" s="7"/>
-    <row r="214" ht="15.75" customHeight="1" s="7"/>
-    <row r="215" ht="15.75" customHeight="1" s="7"/>
-    <row r="216" ht="15.75" customHeight="1" s="7"/>
-    <row r="217" ht="15.75" customHeight="1" s="7"/>
-    <row r="218" ht="15.75" customHeight="1" s="7"/>
-    <row r="219" ht="15.75" customHeight="1" s="7"/>
-    <row r="220" ht="15.75" customHeight="1" s="7"/>
-    <row r="221" ht="15.75" customHeight="1" s="7"/>
-    <row r="222" ht="15.75" customHeight="1" s="7"/>
-    <row r="223" ht="15.75" customHeight="1" s="7"/>
-    <row r="224" ht="15.75" customHeight="1" s="7"/>
-    <row r="225" ht="15.75" customHeight="1" s="7"/>
-    <row r="226" ht="15.75" customHeight="1" s="7"/>
-    <row r="227" ht="15.75" customHeight="1" s="7"/>
-    <row r="228" ht="15.75" customHeight="1" s="7"/>
-    <row r="229" ht="15.75" customHeight="1" s="7"/>
-    <row r="230" ht="15.75" customHeight="1" s="7"/>
-    <row r="231" ht="15.75" customHeight="1" s="7"/>
-    <row r="232" ht="15.75" customHeight="1" s="7"/>
-    <row r="233" ht="15.75" customHeight="1" s="7"/>
-    <row r="234" ht="15.75" customHeight="1" s="7"/>
-    <row r="235" ht="15.75" customHeight="1" s="7"/>
-    <row r="236" ht="15.75" customHeight="1" s="7"/>
-    <row r="237" ht="15.75" customHeight="1" s="7"/>
-    <row r="238" ht="15.75" customHeight="1" s="7"/>
-    <row r="239" ht="15.75" customHeight="1" s="7"/>
-    <row r="240" ht="15.75" customHeight="1" s="7"/>
-    <row r="241" ht="15.75" customHeight="1" s="7"/>
-    <row r="242" ht="15.75" customHeight="1" s="7"/>
-    <row r="243" ht="15.75" customHeight="1" s="7"/>
-    <row r="244" ht="15.75" customHeight="1" s="7"/>
-    <row r="245" ht="15.75" customHeight="1" s="7"/>
-    <row r="246" ht="15.75" customHeight="1" s="7"/>
-    <row r="247" ht="15.75" customHeight="1" s="7"/>
-    <row r="248" ht="15.75" customHeight="1" s="7"/>
-    <row r="249" ht="15.75" customHeight="1" s="7"/>
-    <row r="250" ht="15.75" customHeight="1" s="7"/>
-    <row r="251" ht="15.75" customHeight="1" s="7"/>
-    <row r="252" ht="15.75" customHeight="1" s="7"/>
-    <row r="253" ht="15.75" customHeight="1" s="7"/>
-    <row r="254" ht="15.75" customHeight="1" s="7"/>
-    <row r="255" ht="15.75" customHeight="1" s="7"/>
-    <row r="256" ht="15.75" customHeight="1" s="7"/>
-    <row r="257" ht="15.75" customHeight="1" s="7"/>
-    <row r="258" ht="15.75" customHeight="1" s="7"/>
-    <row r="259" ht="15.75" customHeight="1" s="7"/>
-    <row r="260" ht="15.75" customHeight="1" s="7"/>
-    <row r="261" ht="15.75" customHeight="1" s="7"/>
-    <row r="262" ht="15.75" customHeight="1" s="7"/>
-    <row r="263" ht="15.75" customHeight="1" s="7"/>
-    <row r="264" ht="15.75" customHeight="1" s="7"/>
-    <row r="265" ht="15.75" customHeight="1" s="7"/>
-    <row r="266" ht="15.75" customHeight="1" s="7"/>
-    <row r="267" ht="15.75" customHeight="1" s="7"/>
-    <row r="268" ht="15.75" customHeight="1" s="7"/>
-    <row r="269" ht="15.75" customHeight="1" s="7"/>
-    <row r="270" ht="15.75" customHeight="1" s="7"/>
-    <row r="271" ht="15.75" customHeight="1" s="7"/>
-    <row r="272" ht="15.75" customHeight="1" s="7"/>
-    <row r="273" ht="15.75" customHeight="1" s="7"/>
-    <row r="274" ht="15.75" customHeight="1" s="7"/>
-    <row r="275" ht="15.75" customHeight="1" s="7"/>
-    <row r="276" ht="15.75" customHeight="1" s="7"/>
-    <row r="277" ht="15.75" customHeight="1" s="7"/>
-    <row r="278" ht="15.75" customHeight="1" s="7"/>
-    <row r="279" ht="15.75" customHeight="1" s="7"/>
-    <row r="280" ht="15.75" customHeight="1" s="7"/>
-    <row r="281" ht="15.75" customHeight="1" s="7"/>
-    <row r="282" ht="15.75" customHeight="1" s="7"/>
-    <row r="283" ht="15.75" customHeight="1" s="7"/>
-    <row r="284" ht="15.75" customHeight="1" s="7"/>
-    <row r="285" ht="15.75" customHeight="1" s="7"/>
-    <row r="286" ht="15.75" customHeight="1" s="7"/>
-    <row r="287" ht="15.75" customHeight="1" s="7"/>
-    <row r="288" ht="15.75" customHeight="1" s="7"/>
-    <row r="289" ht="15.75" customHeight="1" s="7"/>
-    <row r="290" ht="15.75" customHeight="1" s="7"/>
-    <row r="291" ht="15.75" customHeight="1" s="7"/>
-    <row r="292" ht="15.75" customHeight="1" s="7"/>
-    <row r="293" ht="15.75" customHeight="1" s="7"/>
-    <row r="294" ht="15.75" customHeight="1" s="7"/>
-    <row r="295" ht="15.75" customHeight="1" s="7"/>
-    <row r="296" ht="15.75" customHeight="1" s="7"/>
-    <row r="297" ht="15.75" customHeight="1" s="7"/>
-    <row r="298" ht="15.75" customHeight="1" s="7"/>
-    <row r="299" ht="15.75" customHeight="1" s="7"/>
-    <row r="300" ht="15.75" customHeight="1" s="7"/>
-    <row r="301" ht="15.75" customHeight="1" s="7"/>
-    <row r="302" ht="15.75" customHeight="1" s="7"/>
-    <row r="303" ht="15.75" customHeight="1" s="7"/>
-    <row r="304" ht="15.75" customHeight="1" s="7"/>
-    <row r="305" ht="15.75" customHeight="1" s="7"/>
-    <row r="306" ht="15.75" customHeight="1" s="7"/>
-    <row r="307" ht="15.75" customHeight="1" s="7"/>
-    <row r="308" ht="15.75" customHeight="1" s="7"/>
-    <row r="309" ht="15.75" customHeight="1" s="7"/>
-    <row r="310" ht="15.75" customHeight="1" s="7"/>
-    <row r="311" ht="15.75" customHeight="1" s="7"/>
-    <row r="312" ht="15.75" customHeight="1" s="7"/>
-    <row r="313" ht="15.75" customHeight="1" s="7"/>
-    <row r="314" ht="15.75" customHeight="1" s="7"/>
-    <row r="315" ht="15.75" customHeight="1" s="7"/>
-    <row r="316" ht="15.75" customHeight="1" s="7"/>
-    <row r="317" ht="15.75" customHeight="1" s="7"/>
-    <row r="318" ht="15.75" customHeight="1" s="7"/>
-    <row r="319" ht="15.75" customHeight="1" s="7"/>
-    <row r="320" ht="15.75" customHeight="1" s="7"/>
-    <row r="321" ht="15.75" customHeight="1" s="7"/>
-    <row r="322" ht="15.75" customHeight="1" s="7"/>
-    <row r="323" ht="15.75" customHeight="1" s="7"/>
-    <row r="324" ht="15.75" customHeight="1" s="7"/>
-    <row r="325" ht="15.75" customHeight="1" s="7"/>
-    <row r="326" ht="15.75" customHeight="1" s="7"/>
-    <row r="327" ht="15.75" customHeight="1" s="7"/>
-    <row r="328" ht="15.75" customHeight="1" s="7"/>
-    <row r="329" ht="15.75" customHeight="1" s="7"/>
-    <row r="330" ht="15.75" customHeight="1" s="7"/>
-    <row r="331" ht="15.75" customHeight="1" s="7"/>
-    <row r="332" ht="15.75" customHeight="1" s="7"/>
-    <row r="333" ht="15.75" customHeight="1" s="7"/>
-    <row r="334" ht="15.75" customHeight="1" s="7"/>
-    <row r="335" ht="15.75" customHeight="1" s="7"/>
-    <row r="336" ht="15.75" customHeight="1" s="7"/>
-    <row r="337" ht="15.75" customHeight="1" s="7"/>
-    <row r="338" ht="15.75" customHeight="1" s="7"/>
-    <row r="339" ht="15.75" customHeight="1" s="7"/>
-    <row r="340" ht="15.75" customHeight="1" s="7"/>
-    <row r="341" ht="15.75" customHeight="1" s="7"/>
-    <row r="342" ht="15.75" customHeight="1" s="7"/>
-    <row r="343" ht="15.75" customHeight="1" s="7"/>
-    <row r="344" ht="15.75" customHeight="1" s="7"/>
-    <row r="345" ht="15.75" customHeight="1" s="7"/>
-    <row r="346" ht="15.75" customHeight="1" s="7"/>
-    <row r="347" ht="15.75" customHeight="1" s="7"/>
-    <row r="348" ht="15.75" customHeight="1" s="7"/>
-    <row r="349" ht="15.75" customHeight="1" s="7"/>
-    <row r="350" ht="15.75" customHeight="1" s="7"/>
-    <row r="351" ht="15.75" customHeight="1" s="7"/>
-    <row r="352" ht="15.75" customHeight="1" s="7"/>
-    <row r="353" ht="15.75" customHeight="1" s="7"/>
-    <row r="354" ht="15.75" customHeight="1" s="7"/>
-    <row r="355" ht="15.75" customHeight="1" s="7"/>
-    <row r="356" ht="15.75" customHeight="1" s="7"/>
-    <row r="357" ht="15.75" customHeight="1" s="7"/>
-    <row r="358" ht="15.75" customHeight="1" s="7"/>
-    <row r="359" ht="15.75" customHeight="1" s="7"/>
-    <row r="360" ht="15.75" customHeight="1" s="7"/>
-    <row r="361" ht="15.75" customHeight="1" s="7"/>
-    <row r="362" ht="15.75" customHeight="1" s="7"/>
-    <row r="363" ht="15.75" customHeight="1" s="7"/>
-    <row r="364" ht="15.75" customHeight="1" s="7"/>
-    <row r="365" ht="15.75" customHeight="1" s="7"/>
-    <row r="366" ht="15.75" customHeight="1" s="7"/>
-    <row r="367" ht="15.75" customHeight="1" s="7"/>
-    <row r="368" ht="15.75" customHeight="1" s="7"/>
-    <row r="369" ht="15.75" customHeight="1" s="7"/>
-    <row r="370" ht="15.75" customHeight="1" s="7"/>
-    <row r="371" ht="15.75" customHeight="1" s="7"/>
-    <row r="372" ht="15.75" customHeight="1" s="7"/>
-    <row r="373" ht="15.75" customHeight="1" s="7"/>
-    <row r="374" ht="15.75" customHeight="1" s="7"/>
-    <row r="375" ht="15.75" customHeight="1" s="7"/>
-    <row r="376" ht="15.75" customHeight="1" s="7"/>
-    <row r="377" ht="15.75" customHeight="1" s="7"/>
-    <row r="378" ht="15.75" customHeight="1" s="7"/>
-    <row r="379" ht="15.75" customHeight="1" s="7"/>
-    <row r="380" ht="15.75" customHeight="1" s="7"/>
-    <row r="381" ht="15.75" customHeight="1" s="7"/>
-    <row r="382" ht="15.75" customHeight="1" s="7"/>
-    <row r="383" ht="15.75" customHeight="1" s="7"/>
-    <row r="384" ht="15.75" customHeight="1" s="7"/>
-    <row r="385" ht="15.75" customHeight="1" s="7"/>
-    <row r="386" ht="15.75" customHeight="1" s="7"/>
-    <row r="387" ht="15.75" customHeight="1" s="7"/>
-    <row r="388" ht="15.75" customHeight="1" s="7"/>
-    <row r="389" ht="15.75" customHeight="1" s="7"/>
-    <row r="390" ht="15.75" customHeight="1" s="7"/>
-    <row r="391" ht="15.75" customHeight="1" s="7"/>
-    <row r="392" ht="15.75" customHeight="1" s="7"/>
-    <row r="393" ht="15.75" customHeight="1" s="7"/>
-    <row r="394" ht="15.75" customHeight="1" s="7"/>
-    <row r="395" ht="15.75" customHeight="1" s="7"/>
-    <row r="396" ht="15.75" customHeight="1" s="7"/>
-    <row r="397" ht="15.75" customHeight="1" s="7"/>
-    <row r="398" ht="15.75" customHeight="1" s="7"/>
-    <row r="399" ht="15.75" customHeight="1" s="7"/>
-    <row r="400" ht="15.75" customHeight="1" s="7"/>
-    <row r="401" ht="15.75" customHeight="1" s="7"/>
-    <row r="402" ht="15.75" customHeight="1" s="7"/>
-    <row r="403" ht="15.75" customHeight="1" s="7"/>
-    <row r="404" ht="15.75" customHeight="1" s="7"/>
-    <row r="405" ht="15.75" customHeight="1" s="7"/>
-    <row r="406" ht="15.75" customHeight="1" s="7"/>
-    <row r="407" ht="15.75" customHeight="1" s="7"/>
-    <row r="408" ht="15.75" customHeight="1" s="7"/>
-    <row r="409" ht="15.75" customHeight="1" s="7"/>
-    <row r="410" ht="15.75" customHeight="1" s="7"/>
-    <row r="411" ht="15.75" customHeight="1" s="7"/>
-    <row r="412" ht="15.75" customHeight="1" s="7"/>
-    <row r="413" ht="15.75" customHeight="1" s="7"/>
-    <row r="414" ht="15.75" customHeight="1" s="7"/>
-    <row r="415" ht="15.75" customHeight="1" s="7"/>
-    <row r="416" ht="15.75" customHeight="1" s="7"/>
-    <row r="417" ht="15.75" customHeight="1" s="7"/>
-    <row r="418" ht="15.75" customHeight="1" s="7"/>
-    <row r="419" ht="15.75" customHeight="1" s="7"/>
-    <row r="420" ht="15.75" customHeight="1" s="7"/>
-    <row r="421" ht="15.75" customHeight="1" s="7"/>
-    <row r="422" ht="15.75" customHeight="1" s="7"/>
-    <row r="423" ht="15.75" customHeight="1" s="7"/>
-    <row r="424" ht="15.75" customHeight="1" s="7"/>
-    <row r="425" ht="15.75" customHeight="1" s="7"/>
-    <row r="426" ht="15.75" customHeight="1" s="7"/>
-    <row r="427" ht="15.75" customHeight="1" s="7"/>
-    <row r="428" ht="15.75" customHeight="1" s="7"/>
-    <row r="429" ht="15.75" customHeight="1" s="7"/>
-    <row r="430" ht="15.75" customHeight="1" s="7"/>
-    <row r="431" ht="15.75" customHeight="1" s="7"/>
-    <row r="432" ht="15.75" customHeight="1" s="7"/>
-    <row r="433" ht="15.75" customHeight="1" s="7"/>
-    <row r="434" ht="15.75" customHeight="1" s="7"/>
-    <row r="435" ht="15.75" customHeight="1" s="7"/>
-    <row r="436" ht="15.75" customHeight="1" s="7"/>
-    <row r="437" ht="15.75" customHeight="1" s="7"/>
-    <row r="438" ht="15.75" customHeight="1" s="7"/>
-    <row r="439" ht="15.75" customHeight="1" s="7"/>
-    <row r="440" ht="15.75" customHeight="1" s="7"/>
-    <row r="441" ht="15.75" customHeight="1" s="7"/>
-    <row r="442" ht="15.75" customHeight="1" s="7"/>
-    <row r="443" ht="15.75" customHeight="1" s="7"/>
-    <row r="444" ht="15.75" customHeight="1" s="7"/>
-    <row r="445" ht="15.75" customHeight="1" s="7"/>
-    <row r="446" ht="15.75" customHeight="1" s="7"/>
-    <row r="447" ht="15.75" customHeight="1" s="7"/>
-    <row r="448" ht="15.75" customHeight="1" s="7"/>
-    <row r="449" ht="15.75" customHeight="1" s="7"/>
-    <row r="450" ht="15.75" customHeight="1" s="7"/>
-    <row r="451" ht="15.75" customHeight="1" s="7"/>
-    <row r="452" ht="15.75" customHeight="1" s="7"/>
-    <row r="453" ht="15.75" customHeight="1" s="7"/>
-    <row r="454" ht="15.75" customHeight="1" s="7"/>
-    <row r="455" ht="15.75" customHeight="1" s="7"/>
-    <row r="456" ht="15.75" customHeight="1" s="7"/>
-    <row r="457" ht="15.75" customHeight="1" s="7"/>
-    <row r="458" ht="15.75" customHeight="1" s="7"/>
-    <row r="459" ht="15.75" customHeight="1" s="7"/>
-    <row r="460" ht="15.75" customHeight="1" s="7"/>
-    <row r="461" ht="15.75" customHeight="1" s="7"/>
-    <row r="462" ht="15.75" customHeight="1" s="7"/>
-    <row r="463" ht="15.75" customHeight="1" s="7"/>
-    <row r="464" ht="15.75" customHeight="1" s="7"/>
-    <row r="465" ht="15.75" customHeight="1" s="7"/>
-    <row r="466" ht="15.75" customHeight="1" s="7"/>
-    <row r="467" ht="15.75" customHeight="1" s="7"/>
-    <row r="468" ht="15.75" customHeight="1" s="7"/>
-    <row r="469" ht="15.75" customHeight="1" s="7"/>
-    <row r="470" ht="15.75" customHeight="1" s="7"/>
-    <row r="471" ht="15.75" customHeight="1" s="7"/>
-    <row r="472" ht="15.75" customHeight="1" s="7"/>
-    <row r="473" ht="15.75" customHeight="1" s="7"/>
-    <row r="474" ht="15.75" customHeight="1" s="7"/>
-    <row r="475" ht="15.75" customHeight="1" s="7"/>
-    <row r="476" ht="15.75" customHeight="1" s="7"/>
-    <row r="477" ht="15.75" customHeight="1" s="7"/>
-    <row r="478" ht="15.75" customHeight="1" s="7"/>
-    <row r="479" ht="15.75" customHeight="1" s="7"/>
-    <row r="480" ht="15.75" customHeight="1" s="7"/>
-    <row r="481" ht="15.75" customHeight="1" s="7"/>
-    <row r="482" ht="15.75" customHeight="1" s="7"/>
-    <row r="483" ht="15.75" customHeight="1" s="7"/>
-    <row r="484" ht="15.75" customHeight="1" s="7"/>
-    <row r="485" ht="15.75" customHeight="1" s="7"/>
-    <row r="486" ht="15.75" customHeight="1" s="7"/>
-    <row r="487" ht="15.75" customHeight="1" s="7"/>
-    <row r="488" ht="15.75" customHeight="1" s="7"/>
-    <row r="489" ht="15.75" customHeight="1" s="7"/>
-    <row r="490" ht="15.75" customHeight="1" s="7"/>
-    <row r="491" ht="15.75" customHeight="1" s="7"/>
-    <row r="492" ht="15.75" customHeight="1" s="7"/>
-    <row r="493" ht="15.75" customHeight="1" s="7"/>
-    <row r="494" ht="15.75" customHeight="1" s="7"/>
-    <row r="495" ht="15.75" customHeight="1" s="7"/>
-    <row r="496" ht="15.75" customHeight="1" s="7"/>
-    <row r="497" ht="15.75" customHeight="1" s="7"/>
-    <row r="498" ht="15.75" customHeight="1" s="7"/>
-    <row r="499" ht="15.75" customHeight="1" s="7"/>
-    <row r="500" ht="15.75" customHeight="1" s="7"/>
-    <row r="501" ht="15.75" customHeight="1" s="7"/>
-    <row r="502" ht="15.75" customHeight="1" s="7"/>
-    <row r="503" ht="15.75" customHeight="1" s="7"/>
-    <row r="504" ht="15.75" customHeight="1" s="7"/>
-    <row r="505" ht="15.75" customHeight="1" s="7"/>
-    <row r="506" ht="15.75" customHeight="1" s="7"/>
-    <row r="507" ht="15.75" customHeight="1" s="7"/>
-    <row r="508" ht="15.75" customHeight="1" s="7"/>
-    <row r="509" ht="15.75" customHeight="1" s="7"/>
-    <row r="510" ht="15.75" customHeight="1" s="7"/>
-    <row r="511" ht="15.75" customHeight="1" s="7"/>
-    <row r="512" ht="15.75" customHeight="1" s="7"/>
-    <row r="513" ht="15.75" customHeight="1" s="7"/>
-    <row r="514" ht="15.75" customHeight="1" s="7"/>
-    <row r="515" ht="15.75" customHeight="1" s="7"/>
-    <row r="516" ht="15.75" customHeight="1" s="7"/>
-    <row r="517" ht="15.75" customHeight="1" s="7"/>
-    <row r="518" ht="15.75" customHeight="1" s="7"/>
-    <row r="519" ht="15.75" customHeight="1" s="7"/>
-    <row r="520" ht="15.75" customHeight="1" s="7"/>
-    <row r="521" ht="15.75" customHeight="1" s="7"/>
-    <row r="522" ht="15.75" customHeight="1" s="7"/>
-    <row r="523" ht="15.75" customHeight="1" s="7"/>
-    <row r="524" ht="15.75" customHeight="1" s="7"/>
-    <row r="525" ht="15.75" customHeight="1" s="7"/>
-    <row r="526" ht="15.75" customHeight="1" s="7"/>
-    <row r="527" ht="15.75" customHeight="1" s="7"/>
-    <row r="528" ht="15.75" customHeight="1" s="7"/>
-    <row r="529" ht="15.75" customHeight="1" s="7"/>
-    <row r="530" ht="15.75" customHeight="1" s="7"/>
-    <row r="531" ht="15.75" customHeight="1" s="7"/>
-    <row r="532" ht="15.75" customHeight="1" s="7"/>
-    <row r="533" ht="15.75" customHeight="1" s="7"/>
-    <row r="534" ht="15.75" customHeight="1" s="7"/>
-    <row r="535" ht="15.75" customHeight="1" s="7"/>
-    <row r="536" ht="15.75" customHeight="1" s="7"/>
-    <row r="537" ht="15.75" customHeight="1" s="7"/>
-    <row r="538" ht="15.75" customHeight="1" s="7"/>
-    <row r="539" ht="15.75" customHeight="1" s="7"/>
-    <row r="540" ht="15.75" customHeight="1" s="7"/>
-    <row r="541" ht="15.75" customHeight="1" s="7"/>
-    <row r="542" ht="15.75" customHeight="1" s="7"/>
-    <row r="543" ht="15.75" customHeight="1" s="7"/>
-    <row r="544" ht="15.75" customHeight="1" s="7"/>
-    <row r="545" ht="15.75" customHeight="1" s="7"/>
-    <row r="546" ht="15.75" customHeight="1" s="7"/>
-    <row r="547" ht="15.75" customHeight="1" s="7"/>
-    <row r="548" ht="15.75" customHeight="1" s="7"/>
-    <row r="549" ht="15.75" customHeight="1" s="7"/>
-    <row r="550" ht="15.75" customHeight="1" s="7"/>
-    <row r="551" ht="15.75" customHeight="1" s="7"/>
-    <row r="552" ht="15.75" customHeight="1" s="7"/>
-    <row r="553" ht="15.75" customHeight="1" s="7"/>
-    <row r="554" ht="15.75" customHeight="1" s="7"/>
-    <row r="555" ht="15.75" customHeight="1" s="7"/>
-    <row r="556" ht="15.75" customHeight="1" s="7"/>
-    <row r="557" ht="15.75" customHeight="1" s="7"/>
-    <row r="558" ht="15.75" customHeight="1" s="7"/>
-    <row r="559" ht="15.75" customHeight="1" s="7"/>
-    <row r="560" ht="15.75" customHeight="1" s="7"/>
-    <row r="561" ht="15.75" customHeight="1" s="7"/>
-    <row r="562" ht="15.75" customHeight="1" s="7"/>
-    <row r="563" ht="15.75" customHeight="1" s="7"/>
-    <row r="564" ht="15.75" customHeight="1" s="7"/>
-    <row r="565" ht="15.75" customHeight="1" s="7"/>
-    <row r="566" ht="15.75" customHeight="1" s="7"/>
-    <row r="567" ht="15.75" customHeight="1" s="7"/>
-    <row r="568" ht="15.75" customHeight="1" s="7"/>
-    <row r="569" ht="15.75" customHeight="1" s="7"/>
-    <row r="570" ht="15.75" customHeight="1" s="7"/>
-    <row r="571" ht="15.75" customHeight="1" s="7"/>
-    <row r="572" ht="15.75" customHeight="1" s="7"/>
-    <row r="573" ht="15.75" customHeight="1" s="7"/>
-    <row r="574" ht="15.75" customHeight="1" s="7"/>
-    <row r="575" ht="15.75" customHeight="1" s="7"/>
-    <row r="576" ht="15.75" customHeight="1" s="7"/>
-    <row r="577" ht="15.75" customHeight="1" s="7"/>
-    <row r="578" ht="15.75" customHeight="1" s="7"/>
-    <row r="579" ht="15.75" customHeight="1" s="7"/>
-    <row r="580" ht="15.75" customHeight="1" s="7"/>
-    <row r="581" ht="15.75" customHeight="1" s="7"/>
-    <row r="582" ht="15.75" customHeight="1" s="7"/>
-    <row r="583" ht="15.75" customHeight="1" s="7"/>
-    <row r="584" ht="15.75" customHeight="1" s="7"/>
-    <row r="585" ht="15.75" customHeight="1" s="7"/>
-    <row r="586" ht="15.75" customHeight="1" s="7"/>
-    <row r="587" ht="15.75" customHeight="1" s="7"/>
-    <row r="588" ht="15.75" customHeight="1" s="7"/>
-    <row r="589" ht="15.75" customHeight="1" s="7"/>
-    <row r="590" ht="15.75" customHeight="1" s="7"/>
-    <row r="591" ht="15.75" customHeight="1" s="7"/>
-    <row r="592" ht="15.75" customHeight="1" s="7"/>
-    <row r="593" ht="15.75" customHeight="1" s="7"/>
-    <row r="594" ht="15.75" customHeight="1" s="7"/>
-    <row r="595" ht="15.75" customHeight="1" s="7"/>
-    <row r="596" ht="15.75" customHeight="1" s="7"/>
-    <row r="597" ht="15.75" customHeight="1" s="7"/>
-    <row r="598" ht="15.75" customHeight="1" s="7"/>
-    <row r="599" ht="15.75" customHeight="1" s="7"/>
-    <row r="600" ht="15.75" customHeight="1" s="7"/>
-    <row r="601" ht="15.75" customHeight="1" s="7"/>
-    <row r="602" ht="15.75" customHeight="1" s="7"/>
-    <row r="603" ht="15.75" customHeight="1" s="7"/>
-    <row r="604" ht="15.75" customHeight="1" s="7"/>
-    <row r="605" ht="15.75" customHeight="1" s="7"/>
-    <row r="606" ht="15.75" customHeight="1" s="7"/>
-    <row r="607" ht="15.75" customHeight="1" s="7"/>
-    <row r="608" ht="15.75" customHeight="1" s="7"/>
-    <row r="609" ht="15.75" customHeight="1" s="7"/>
-    <row r="610" ht="15.75" customHeight="1" s="7"/>
-    <row r="611" ht="15.75" customHeight="1" s="7"/>
-    <row r="612" ht="15.75" customHeight="1" s="7"/>
-    <row r="613" ht="15.75" customHeight="1" s="7"/>
-    <row r="614" ht="15.75" customHeight="1" s="7"/>
-    <row r="615" ht="15.75" customHeight="1" s="7"/>
-    <row r="616" ht="15.75" customHeight="1" s="7"/>
-    <row r="617" ht="15.75" customHeight="1" s="7"/>
-    <row r="618" ht="15.75" customHeight="1" s="7"/>
-    <row r="619" ht="15.75" customHeight="1" s="7"/>
-    <row r="620" ht="15.75" customHeight="1" s="7"/>
-    <row r="621" ht="15.75" customHeight="1" s="7"/>
-    <row r="622" ht="15.75" customHeight="1" s="7"/>
-    <row r="623" ht="15.75" customHeight="1" s="7"/>
-    <row r="624" ht="15.75" customHeight="1" s="7"/>
-    <row r="625" ht="15.75" customHeight="1" s="7"/>
-    <row r="626" ht="15.75" customHeight="1" s="7"/>
-    <row r="627" ht="15.75" customHeight="1" s="7"/>
-    <row r="628" ht="15.75" customHeight="1" s="7"/>
-    <row r="629" ht="15.75" customHeight="1" s="7"/>
-    <row r="630" ht="15.75" customHeight="1" s="7"/>
-    <row r="631" ht="15.75" customHeight="1" s="7"/>
-    <row r="632" ht="15.75" customHeight="1" s="7"/>
-    <row r="633" ht="15.75" customHeight="1" s="7"/>
-    <row r="634" ht="15.75" customHeight="1" s="7"/>
-    <row r="635" ht="15.75" customHeight="1" s="7"/>
-    <row r="636" ht="15.75" customHeight="1" s="7"/>
-    <row r="637" ht="15.75" customHeight="1" s="7"/>
-    <row r="638" ht="15.75" customHeight="1" s="7"/>
-    <row r="639" ht="15.75" customHeight="1" s="7"/>
-    <row r="640" ht="15.75" customHeight="1" s="7"/>
-    <row r="641" ht="15.75" customHeight="1" s="7"/>
-    <row r="642" ht="15.75" customHeight="1" s="7"/>
-    <row r="643" ht="15.75" customHeight="1" s="7"/>
-    <row r="644" ht="15.75" customHeight="1" s="7"/>
-    <row r="645" ht="15.75" customHeight="1" s="7"/>
-    <row r="646" ht="15.75" customHeight="1" s="7"/>
-    <row r="647" ht="15.75" customHeight="1" s="7"/>
-    <row r="648" ht="15.75" customHeight="1" s="7"/>
-    <row r="649" ht="15.75" customHeight="1" s="7"/>
-    <row r="650" ht="15.75" customHeight="1" s="7"/>
-    <row r="651" ht="15.75" customHeight="1" s="7"/>
-    <row r="652" ht="15.75" customHeight="1" s="7"/>
-    <row r="653" ht="15.75" customHeight="1" s="7"/>
-    <row r="654" ht="15.75" customHeight="1" s="7"/>
-    <row r="655" ht="15.75" customHeight="1" s="7"/>
-    <row r="656" ht="15.75" customHeight="1" s="7"/>
-    <row r="657" ht="15.75" customHeight="1" s="7"/>
-    <row r="658" ht="15.75" customHeight="1" s="7"/>
-    <row r="659" ht="15.75" customHeight="1" s="7"/>
-    <row r="660" ht="15.75" customHeight="1" s="7"/>
-    <row r="661" ht="15.75" customHeight="1" s="7"/>
-    <row r="662" ht="15.75" customHeight="1" s="7"/>
-    <row r="663" ht="15.75" customHeight="1" s="7"/>
-    <row r="664" ht="15.75" customHeight="1" s="7"/>
-    <row r="665" ht="15.75" customHeight="1" s="7"/>
-    <row r="666" ht="15.75" customHeight="1" s="7"/>
-    <row r="667" ht="15.75" customHeight="1" s="7"/>
-    <row r="668" ht="15.75" customHeight="1" s="7"/>
-    <row r="669" ht="15.75" customHeight="1" s="7"/>
-    <row r="670" ht="15.75" customHeight="1" s="7"/>
-    <row r="671" ht="15.75" customHeight="1" s="7"/>
-    <row r="672" ht="15.75" customHeight="1" s="7"/>
-    <row r="673" ht="15.75" customHeight="1" s="7"/>
-    <row r="674" ht="15.75" customHeight="1" s="7"/>
-    <row r="675" ht="15.75" customHeight="1" s="7"/>
-    <row r="676" ht="15.75" customHeight="1" s="7"/>
-    <row r="677" ht="15.75" customHeight="1" s="7"/>
-    <row r="678" ht="15.75" customHeight="1" s="7"/>
-    <row r="679" ht="15.75" customHeight="1" s="7"/>
-    <row r="680" ht="15.75" customHeight="1" s="7"/>
-    <row r="681" ht="15.75" customHeight="1" s="7"/>
-    <row r="682" ht="15.75" customHeight="1" s="7"/>
-    <row r="683" ht="15.75" customHeight="1" s="7"/>
-    <row r="684" ht="15.75" customHeight="1" s="7"/>
-    <row r="685" ht="15.75" customHeight="1" s="7"/>
-    <row r="686" ht="15.75" customHeight="1" s="7"/>
-    <row r="687" ht="15.75" customHeight="1" s="7"/>
-    <row r="688" ht="15.75" customHeight="1" s="7"/>
-    <row r="689" ht="15.75" customHeight="1" s="7"/>
-    <row r="690" ht="15.75" customHeight="1" s="7"/>
-    <row r="691" ht="15.75" customHeight="1" s="7"/>
-    <row r="692" ht="15.75" customHeight="1" s="7"/>
-    <row r="693" ht="15.75" customHeight="1" s="7"/>
-    <row r="694" ht="15.75" customHeight="1" s="7"/>
-    <row r="695" ht="15.75" customHeight="1" s="7"/>
-    <row r="696" ht="15.75" customHeight="1" s="7"/>
-    <row r="697" ht="15.75" customHeight="1" s="7"/>
-    <row r="698" ht="15.75" customHeight="1" s="7"/>
-    <row r="699" ht="15.75" customHeight="1" s="7"/>
-    <row r="700" ht="15.75" customHeight="1" s="7"/>
-    <row r="701" ht="15.75" customHeight="1" s="7"/>
-    <row r="702" ht="15.75" customHeight="1" s="7"/>
-    <row r="703" ht="15.75" customHeight="1" s="7"/>
-    <row r="704" ht="15.75" customHeight="1" s="7"/>
-    <row r="705" ht="15.75" customHeight="1" s="7"/>
-    <row r="706" ht="15.75" customHeight="1" s="7"/>
-    <row r="707" ht="15.75" customHeight="1" s="7"/>
-    <row r="708" ht="15.75" customHeight="1" s="7"/>
-    <row r="709" ht="15.75" customHeight="1" s="7"/>
-    <row r="710" ht="15.75" customHeight="1" s="7"/>
-    <row r="711" ht="15.75" customHeight="1" s="7"/>
-    <row r="712" ht="15.75" customHeight="1" s="7"/>
-    <row r="713" ht="15.75" customHeight="1" s="7"/>
-    <row r="714" ht="15.75" customHeight="1" s="7"/>
-    <row r="715" ht="15.75" customHeight="1" s="7"/>
-    <row r="716" ht="15.75" customHeight="1" s="7"/>
-    <row r="717" ht="15.75" customHeight="1" s="7"/>
-    <row r="718" ht="15.75" customHeight="1" s="7"/>
-    <row r="719" ht="15.75" customHeight="1" s="7"/>
-    <row r="720" ht="15.75" customHeight="1" s="7"/>
-    <row r="721" ht="15.75" customHeight="1" s="7"/>
-    <row r="722" ht="15.75" customHeight="1" s="7"/>
-    <row r="723" ht="15.75" customHeight="1" s="7"/>
-    <row r="724" ht="15.75" customHeight="1" s="7"/>
-    <row r="725" ht="15.75" customHeight="1" s="7"/>
-    <row r="726" ht="15.75" customHeight="1" s="7"/>
-    <row r="727" ht="15.75" customHeight="1" s="7"/>
-    <row r="728" ht="15.75" customHeight="1" s="7"/>
-    <row r="729" ht="15.75" customHeight="1" s="7"/>
-    <row r="730" ht="15.75" customHeight="1" s="7"/>
-    <row r="731" ht="15.75" customHeight="1" s="7"/>
-    <row r="732" ht="15.75" customHeight="1" s="7"/>
-    <row r="733" ht="15.75" customHeight="1" s="7"/>
-    <row r="734" ht="15.75" customHeight="1" s="7"/>
-    <row r="735" ht="15.75" customHeight="1" s="7"/>
-    <row r="736" ht="15.75" customHeight="1" s="7"/>
-    <row r="737" ht="15.75" customHeight="1" s="7"/>
-    <row r="738" ht="15.75" customHeight="1" s="7"/>
-    <row r="739" ht="15.75" customHeight="1" s="7"/>
-    <row r="740" ht="15.75" customHeight="1" s="7"/>
-    <row r="741" ht="15.75" customHeight="1" s="7"/>
-    <row r="742" ht="15.75" customHeight="1" s="7"/>
-    <row r="743" ht="15.75" customHeight="1" s="7"/>
-    <row r="744" ht="15.75" customHeight="1" s="7"/>
-    <row r="745" ht="15.75" customHeight="1" s="7"/>
-    <row r="746" ht="15.75" customHeight="1" s="7"/>
-    <row r="747" ht="15.75" customHeight="1" s="7"/>
-    <row r="748" ht="15.75" customHeight="1" s="7"/>
-    <row r="749" ht="15.75" customHeight="1" s="7"/>
-    <row r="750" ht="15.75" customHeight="1" s="7"/>
-    <row r="751" ht="15.75" customHeight="1" s="7"/>
-    <row r="752" ht="15.75" customHeight="1" s="7"/>
-    <row r="753" ht="15.75" customHeight="1" s="7"/>
-    <row r="754" ht="15.75" customHeight="1" s="7"/>
-    <row r="755" ht="15.75" customHeight="1" s="7"/>
-    <row r="756" ht="15.75" customHeight="1" s="7"/>
-    <row r="757" ht="15.75" customHeight="1" s="7"/>
-    <row r="758" ht="15.75" customHeight="1" s="7"/>
-    <row r="759" ht="15.75" customHeight="1" s="7"/>
-    <row r="760" ht="15.75" customHeight="1" s="7"/>
-    <row r="761" ht="15.75" customHeight="1" s="7"/>
-    <row r="762" ht="15.75" customHeight="1" s="7"/>
-    <row r="763" ht="15.75" customHeight="1" s="7"/>
-    <row r="764" ht="15.75" customHeight="1" s="7"/>
-    <row r="765" ht="15.75" customHeight="1" s="7"/>
-    <row r="766" ht="15.75" customHeight="1" s="7"/>
-    <row r="767" ht="15.75" customHeight="1" s="7"/>
-    <row r="768" ht="15.75" customHeight="1" s="7"/>
-    <row r="769" ht="15.75" customHeight="1" s="7"/>
-    <row r="770" ht="15.75" customHeight="1" s="7"/>
-    <row r="771" ht="15.75" customHeight="1" s="7"/>
-    <row r="772" ht="15.75" customHeight="1" s="7"/>
-    <row r="773" ht="15.75" customHeight="1" s="7"/>
-    <row r="774" ht="15.75" customHeight="1" s="7"/>
-    <row r="775" ht="15.75" customHeight="1" s="7"/>
-    <row r="776" ht="15.75" customHeight="1" s="7"/>
-    <row r="777" ht="15.75" customHeight="1" s="7"/>
-    <row r="778" ht="15.75" customHeight="1" s="7"/>
-    <row r="779" ht="15.75" customHeight="1" s="7"/>
-    <row r="780" ht="15.75" customHeight="1" s="7"/>
-    <row r="781" ht="15.75" customHeight="1" s="7"/>
-    <row r="782" ht="15.75" customHeight="1" s="7"/>
-    <row r="783" ht="15.75" customHeight="1" s="7"/>
-    <row r="784" ht="15.75" customHeight="1" s="7"/>
-    <row r="785" ht="15.75" customHeight="1" s="7"/>
-    <row r="786" ht="15.75" customHeight="1" s="7"/>
-    <row r="787" ht="15.75" customHeight="1" s="7"/>
-    <row r="788" ht="15.75" customHeight="1" s="7"/>
-    <row r="789" ht="15.75" customHeight="1" s="7"/>
-    <row r="790" ht="15.75" customHeight="1" s="7"/>
-    <row r="791" ht="15.75" customHeight="1" s="7"/>
-    <row r="792" ht="15.75" customHeight="1" s="7"/>
-    <row r="793" ht="15.75" customHeight="1" s="7"/>
-    <row r="794" ht="15.75" customHeight="1" s="7"/>
-    <row r="795" ht="15.75" customHeight="1" s="7"/>
-    <row r="796" ht="15.75" customHeight="1" s="7"/>
-    <row r="797" ht="15.75" customHeight="1" s="7"/>
-    <row r="798" ht="15.75" customHeight="1" s="7"/>
-    <row r="799" ht="15.75" customHeight="1" s="7"/>
-    <row r="800" ht="15.75" customHeight="1" s="7"/>
-    <row r="801" ht="15.75" customHeight="1" s="7"/>
-    <row r="802" ht="15.75" customHeight="1" s="7"/>
-    <row r="803" ht="15.75" customHeight="1" s="7"/>
-    <row r="804" ht="15.75" customHeight="1" s="7"/>
-    <row r="805" ht="15.75" customHeight="1" s="7"/>
-    <row r="806" ht="15.75" customHeight="1" s="7"/>
-    <row r="807" ht="15.75" customHeight="1" s="7"/>
-    <row r="808" ht="15.75" customHeight="1" s="7"/>
-    <row r="809" ht="15.75" customHeight="1" s="7"/>
-    <row r="810" ht="15.75" customHeight="1" s="7"/>
-    <row r="811" ht="15.75" customHeight="1" s="7"/>
-    <row r="812" ht="15.75" customHeight="1" s="7"/>
-    <row r="813" ht="15.75" customHeight="1" s="7"/>
-    <row r="814" ht="15.75" customHeight="1" s="7"/>
-    <row r="815" ht="15.75" customHeight="1" s="7"/>
-    <row r="816" ht="15.75" customHeight="1" s="7"/>
-    <row r="817" ht="15.75" customHeight="1" s="7"/>
-    <row r="818" ht="15.75" customHeight="1" s="7"/>
-    <row r="819" ht="15.75" customHeight="1" s="7"/>
-    <row r="820" ht="15.75" customHeight="1" s="7"/>
-    <row r="821" ht="15.75" customHeight="1" s="7"/>
-    <row r="822" ht="15.75" customHeight="1" s="7"/>
-    <row r="823" ht="15.75" customHeight="1" s="7"/>
-    <row r="824" ht="15.75" customHeight="1" s="7"/>
-    <row r="825" ht="15.75" customHeight="1" s="7"/>
-    <row r="826" ht="15.75" customHeight="1" s="7"/>
-    <row r="827" ht="15.75" customHeight="1" s="7"/>
-    <row r="828" ht="15.75" customHeight="1" s="7"/>
-    <row r="829" ht="15.75" customHeight="1" s="7"/>
-    <row r="830" ht="15.75" customHeight="1" s="7"/>
-    <row r="831" ht="15.75" customHeight="1" s="7"/>
-    <row r="832" ht="15.75" customHeight="1" s="7"/>
-    <row r="833" ht="15.75" customHeight="1" s="7"/>
-    <row r="834" ht="15.75" customHeight="1" s="7"/>
-    <row r="835" ht="15.75" customHeight="1" s="7"/>
-    <row r="836" ht="15.75" customHeight="1" s="7"/>
-    <row r="837" ht="15.75" customHeight="1" s="7"/>
-    <row r="838" ht="15.75" customHeight="1" s="7"/>
-    <row r="839" ht="15.75" customHeight="1" s="7"/>
-    <row r="840" ht="15.75" customHeight="1" s="7"/>
-    <row r="841" ht="15.75" customHeight="1" s="7"/>
-    <row r="842" ht="15.75" customHeight="1" s="7"/>
-    <row r="843" ht="15.75" customHeight="1" s="7"/>
-    <row r="844" ht="15.75" customHeight="1" s="7"/>
-    <row r="845" ht="15.75" customHeight="1" s="7"/>
-    <row r="846" ht="15.75" customHeight="1" s="7"/>
-    <row r="847" ht="15.75" customHeight="1" s="7"/>
-    <row r="848" ht="15.75" customHeight="1" s="7"/>
-    <row r="849" ht="15.75" customHeight="1" s="7"/>
-    <row r="850" ht="15.75" customHeight="1" s="7"/>
-    <row r="851" ht="15.75" customHeight="1" s="7"/>
-    <row r="852" ht="15.75" customHeight="1" s="7"/>
-    <row r="853" ht="15.75" customHeight="1" s="7"/>
-    <row r="854" ht="15.75" customHeight="1" s="7"/>
-    <row r="855" ht="15.75" customHeight="1" s="7"/>
-    <row r="856" ht="15.75" customHeight="1" s="7"/>
-    <row r="857" ht="15.75" customHeight="1" s="7"/>
-    <row r="858" ht="15.75" customHeight="1" s="7"/>
-    <row r="859" ht="15.75" customHeight="1" s="7"/>
-    <row r="860" ht="15.75" customHeight="1" s="7"/>
-    <row r="861" ht="15.75" customHeight="1" s="7"/>
-    <row r="862" ht="15.75" customHeight="1" s="7"/>
-    <row r="863" ht="15.75" customHeight="1" s="7"/>
-    <row r="864" ht="15.75" customHeight="1" s="7"/>
-    <row r="865" ht="15.75" customHeight="1" s="7"/>
-    <row r="866" ht="15.75" customHeight="1" s="7"/>
-    <row r="867" ht="15.75" customHeight="1" s="7"/>
-    <row r="868" ht="15.75" customHeight="1" s="7"/>
-    <row r="869" ht="15.75" customHeight="1" s="7"/>
-    <row r="870" ht="15.75" customHeight="1" s="7"/>
-    <row r="871" ht="15.75" customHeight="1" s="7"/>
-    <row r="872" ht="15.75" customHeight="1" s="7"/>
-    <row r="873" ht="15.75" customHeight="1" s="7"/>
-    <row r="874" ht="15.75" customHeight="1" s="7"/>
-    <row r="875" ht="15.75" customHeight="1" s="7"/>
-    <row r="876" ht="15.75" customHeight="1" s="7"/>
-    <row r="877" ht="15.75" customHeight="1" s="7"/>
-    <row r="878" ht="15.75" customHeight="1" s="7"/>
-    <row r="879" ht="15.75" customHeight="1" s="7"/>
-    <row r="880" ht="15.75" customHeight="1" s="7"/>
-    <row r="881" ht="15.75" customHeight="1" s="7"/>
-    <row r="882" ht="15.75" customHeight="1" s="7"/>
-    <row r="883" ht="15.75" customHeight="1" s="7"/>
-    <row r="884" ht="15.75" customHeight="1" s="7"/>
-    <row r="885" ht="15.75" customHeight="1" s="7"/>
-    <row r="886" ht="15.75" customHeight="1" s="7"/>
-    <row r="887" ht="15.75" customHeight="1" s="7"/>
-    <row r="888" ht="15.75" customHeight="1" s="7"/>
-    <row r="889" ht="15.75" customHeight="1" s="7"/>
-    <row r="890" ht="15.75" customHeight="1" s="7"/>
-    <row r="891" ht="15.75" customHeight="1" s="7"/>
-    <row r="892" ht="15.75" customHeight="1" s="7"/>
-    <row r="893" ht="15.75" customHeight="1" s="7"/>
-    <row r="894" ht="15.75" customHeight="1" s="7"/>
-    <row r="895" ht="15.75" customHeight="1" s="7"/>
-    <row r="896" ht="15.75" customHeight="1" s="7"/>
-    <row r="897" ht="15.75" customHeight="1" s="7"/>
-    <row r="898" ht="15.75" customHeight="1" s="7"/>
-    <row r="899" ht="15.75" customHeight="1" s="7"/>
-    <row r="900" ht="15.75" customHeight="1" s="7"/>
-    <row r="901" ht="15.75" customHeight="1" s="7"/>
-    <row r="902" ht="15.75" customHeight="1" s="7"/>
-    <row r="903" ht="15.75" customHeight="1" s="7"/>
-    <row r="904" ht="15.75" customHeight="1" s="7"/>
-    <row r="905" ht="15.75" customHeight="1" s="7"/>
-    <row r="906" ht="15.75" customHeight="1" s="7"/>
-    <row r="907" ht="15.75" customHeight="1" s="7"/>
-    <row r="908" ht="15.75" customHeight="1" s="7"/>
-    <row r="909" ht="15.75" customHeight="1" s="7"/>
-    <row r="910" ht="15.75" customHeight="1" s="7"/>
-    <row r="911" ht="15.75" customHeight="1" s="7"/>
-    <row r="912" ht="15.75" customHeight="1" s="7"/>
-    <row r="913" ht="15.75" customHeight="1" s="7"/>
-    <row r="914" ht="15.75" customHeight="1" s="7"/>
-    <row r="915" ht="15.75" customHeight="1" s="7"/>
-    <row r="916" ht="15.75" customHeight="1" s="7"/>
-    <row r="917" ht="15.75" customHeight="1" s="7"/>
-    <row r="918" ht="15.75" customHeight="1" s="7"/>
-    <row r="919" ht="15.75" customHeight="1" s="7"/>
-    <row r="920" ht="15.75" customHeight="1" s="7"/>
-    <row r="921" ht="15.75" customHeight="1" s="7"/>
-    <row r="922" ht="15.75" customHeight="1" s="7"/>
-    <row r="923" ht="15.75" customHeight="1" s="7"/>
-    <row r="924" ht="15.75" customHeight="1" s="7"/>
-    <row r="925" ht="15.75" customHeight="1" s="7"/>
-    <row r="926" ht="15.75" customHeight="1" s="7"/>
-    <row r="927" ht="15.75" customHeight="1" s="7"/>
-    <row r="928" ht="15.75" customHeight="1" s="7"/>
-    <row r="929" ht="15.75" customHeight="1" s="7"/>
-    <row r="930" ht="15.75" customHeight="1" s="7"/>
-    <row r="931" ht="15.75" customHeight="1" s="7"/>
-    <row r="932" ht="15.75" customHeight="1" s="7"/>
-    <row r="933" ht="15.75" customHeight="1" s="7"/>
-    <row r="934" ht="15.75" customHeight="1" s="7"/>
-    <row r="935" ht="15.75" customHeight="1" s="7"/>
-    <row r="936" ht="15.75" customHeight="1" s="7"/>
-    <row r="937" ht="15.75" customHeight="1" s="7"/>
-    <row r="938" ht="15.75" customHeight="1" s="7"/>
-    <row r="939" ht="15.75" customHeight="1" s="7"/>
-    <row r="940" ht="15.75" customHeight="1" s="7"/>
-    <row r="941" ht="15.75" customHeight="1" s="7"/>
-    <row r="942" ht="15.75" customHeight="1" s="7"/>
-    <row r="943" ht="15.75" customHeight="1" s="7"/>
-    <row r="944" ht="15.75" customHeight="1" s="7"/>
-    <row r="945" ht="15.75" customHeight="1" s="7"/>
-    <row r="946" ht="15.75" customHeight="1" s="7"/>
-    <row r="947" ht="15.75" customHeight="1" s="7"/>
-    <row r="948" ht="15.75" customHeight="1" s="7"/>
-    <row r="949" ht="15.75" customHeight="1" s="7"/>
-    <row r="950" ht="15.75" customHeight="1" s="7"/>
-    <row r="951" ht="15.75" customHeight="1" s="7"/>
-    <row r="952" ht="15.75" customHeight="1" s="7"/>
-    <row r="953" ht="15.75" customHeight="1" s="7"/>
-    <row r="954" ht="15.75" customHeight="1" s="7"/>
-    <row r="955" ht="15.75" customHeight="1" s="7"/>
-    <row r="956" ht="15.75" customHeight="1" s="7"/>
-    <row r="957" ht="15.75" customHeight="1" s="7"/>
-    <row r="958" ht="15.75" customHeight="1" s="7"/>
-    <row r="959" ht="15.75" customHeight="1" s="7"/>
-    <row r="960" ht="15.75" customHeight="1" s="7"/>
-    <row r="961" ht="15.75" customHeight="1" s="7"/>
-    <row r="962" ht="15.75" customHeight="1" s="7"/>
-    <row r="963" ht="15.75" customHeight="1" s="7"/>
-    <row r="964" ht="15.75" customHeight="1" s="7"/>
-    <row r="965" ht="15.75" customHeight="1" s="7"/>
-    <row r="966" ht="15.75" customHeight="1" s="7"/>
-    <row r="967" ht="15.75" customHeight="1" s="7"/>
-    <row r="968" ht="15.75" customHeight="1" s="7"/>
-    <row r="969" ht="15.75" customHeight="1" s="7"/>
-    <row r="970" ht="15.75" customHeight="1" s="7"/>
-    <row r="971" ht="15.75" customHeight="1" s="7"/>
-    <row r="972" ht="15.75" customHeight="1" s="7"/>
-    <row r="973" ht="15.75" customHeight="1" s="7"/>
-    <row r="974" ht="15.75" customHeight="1" s="7"/>
-    <row r="975" ht="15.75" customHeight="1" s="7"/>
-    <row r="976" ht="15.75" customHeight="1" s="7"/>
-    <row r="977" ht="15.75" customHeight="1" s="7"/>
-    <row r="978" ht="15.75" customHeight="1" s="7"/>
-    <row r="979" ht="15.75" customHeight="1" s="7"/>
-    <row r="980" ht="15.75" customHeight="1" s="7"/>
-    <row r="981" ht="15.75" customHeight="1" s="7"/>
-    <row r="982" ht="15.75" customHeight="1" s="7"/>
-    <row r="983" ht="15.75" customHeight="1" s="7"/>
-    <row r="984" ht="15.75" customHeight="1" s="7"/>
-    <row r="985" ht="15.75" customHeight="1" s="7"/>
-    <row r="986" ht="15.75" customHeight="1" s="7"/>
-    <row r="987" ht="15.75" customHeight="1" s="7"/>
-    <row r="988" ht="15.75" customHeight="1" s="7"/>
-    <row r="989" ht="15.75" customHeight="1" s="7"/>
-    <row r="990" ht="15.75" customHeight="1" s="7"/>
-    <row r="991" ht="15.75" customHeight="1" s="7"/>
-    <row r="992" ht="15.75" customHeight="1" s="7"/>
-    <row r="993" ht="15.75" customHeight="1" s="7"/>
-    <row r="994" ht="15.75" customHeight="1" s="7"/>
-    <row r="995" ht="15.75" customHeight="1" s="7"/>
-    <row r="996" ht="15.75" customHeight="1" s="7"/>
-    <row r="997" ht="15.75" customHeight="1" s="7"/>
-    <row r="998" ht="15.75" customHeight="1" s="7"/>
-    <row r="999" ht="15.75" customHeight="1" s="7"/>
-    <row r="1000" ht="15.75" customHeight="1" s="7"/>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="D14:D17"/>
-    <mergeCell ref="C18:C23"/>
-    <mergeCell ref="B18:B23"/>
-    <mergeCell ref="D18:D23"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="B2:B7"/>
-    <mergeCell ref="C2:C7"/>
-    <mergeCell ref="D2:D7"/>
-    <mergeCell ref="D11:D12"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Conversation_List/Conversation_List_Test_Cases.xlsx
+++ b/Conversation_List/Conversation_List_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -693,146 +693,102 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>CL_007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Verify User and Group Listing</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>User is logged in with no conversations</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify empty conversation list state</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Login with new account.
 2. Navigate to Chats.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Empty state message should display.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CL_008</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete Conversation</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and has conversations</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Verify delete icon appears on swipe/hover</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1. Swipe left on conversation (mobile) or hover (desktop).</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Delete icon (trash) should appear.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CL_009</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="n"/>
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Verify delete confirmation dialog</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1. Click delete icon on conversation.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Confirmation dialog should appear.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CL_010</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
+          <t>CL_008</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete Conversation</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and delete dialog shown</t>
+          <t>User is logged in and has conversations</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Verify conversation deleted on confirm</t>
+          <t>Verify delete icon appears on swipe/hover</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1. Click confirm in delete dialog.</t>
+          <t>1. Swipe left on conversation (mobile) or hover (desktop).</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Conversation should be removed from list.</t>
+          <t>Delete icon (trash) should appear.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -844,7 +800,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CL_011</t>
+          <t>CL_009</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -852,60 +808,51 @@
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify cancel delete keeps conversation</t>
+          <t>Verify delete confirmation dialog</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1. Click cancel in delete dialog.</t>
+          <t>1. Click delete icon on conversation.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Conversation should remain in list.</t>
+          <t>Confirmation dialog should appear.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CL_012</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete Conversation</t>
-        </is>
-      </c>
+          <t>CL_010</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, network disconnected</t>
+          <t>User is logged in and delete dialog shown</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify delete fails without network</t>
+          <t>Verify conversation deleted on confirm</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1. Disconnect network.
-2. Try to delete conversation.</t>
+          <t>1. Click confirm in delete dialog.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Error message should display.</t>
+          <t>Conversation should be removed from list.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -917,97 +864,78 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CL_013</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Verify Check Day</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and has conversations</t>
-        </is>
-      </c>
+          <t>CL_011</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify today's conversation shows time</t>
+          <t>Verify cancel delete keeps conversation</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1. Observe conversation from today.</t>
+          <t>1. Click cancel in delete dialog.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Time should display (e.g., "02:35 AM").</t>
+          <t>Conversation should remain in list.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CL_014</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="n"/>
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Verify yesterday's conversation shows 'Yesterday'</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1. Observe conversation from yesterday.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>"Yesterday" should display instead of date.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CL_015</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
+          <t>CL_012</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete Conversation</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify older conversation shows date</t>
+          <t>Verify delete fails without network</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1. Observe conversation older than yesterday.</t>
+          <t>1. Disconnect network.
+2. Try to delete conversation.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Date should display (e.g., "05/02/2026").</t>
+          <t>Error message should display.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1017,40 +945,19 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CL_016</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="n"/>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Verify date updates after midnight</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1. Check conversation at 11:59 PM.
-2. Check again after midnight.</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Date/time label should update appropriately.</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CL_017</t>
+          <t>CL_013</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1060,7 +967,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Verify Preview Message</t>
+          <t>Verify Check Day</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1070,17 +977,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify last message preview displays</t>
+          <t>Verify today's conversation shows time</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1. Observe conversation in list.</t>
+          <t>1. Observe conversation from today.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Last message preview should display below name.</t>
+          <t>Time should display (e.g., "02:35 AM").</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1092,7 +999,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CL_018</t>
+          <t>CL_014</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
@@ -1100,18 +1007,17 @@
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify 'You:' prefix for sent messages</t>
+          <t>Verify yesterday's conversation shows 'Yesterday'</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1. Send message.
-2. Observe conversation preview.</t>
+          <t>1. Observe conversation from yesterday.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Preview should show "You: [message]" for sent messages.</t>
+          <t>"Yesterday" should display instead of date.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1123,7 +1029,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CL_019</t>
+          <t>CL_015</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
@@ -1131,17 +1037,17 @@
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify message status checkmark</t>
+          <t>Verify older conversation shows date</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1. Observe sent message preview.</t>
+          <t>1. Observe conversation older than yesterday.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Checkmark should display (single=sent, double=delivered).</t>
+          <t>Date should display (e.g., "05/02/2026").</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1153,7 +1059,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CL_020</t>
+          <t>CL_016</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
@@ -1161,18 +1067,18 @@
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify long message truncation</t>
+          <t>Verify date updates after midnight</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1. Send long message.
-2. Observe preview.</t>
+          <t>1. Check conversation at 11:59 PM.
+2. Check again after midnight.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Long message should be truncated with ellipsis.</t>
+          <t>Date/time label should update appropriately.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1184,38 +1090,49 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CL_021</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
+          <t>CL_017</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Verify Preview Message</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and has conversations</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify image/attachment preview</t>
+          <t>Verify last message preview displays</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1. Send image.
-2. Observe preview.</t>
+          <t>1. Observe conversation in list.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Preview should show attachment indicator (e.g., "📷 Photo").</t>
+          <t>Last message preview should display below name.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CL_022</t>
+          <t>CL_018</t>
         </is>
       </c>
       <c r="B23" s="2" t="n"/>
@@ -1223,106 +1140,249 @@
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>Verify 'You:' prefix for sent messages</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1. Send message.
+2. Observe conversation preview.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Preview should show "You: [message]" for sent messages.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>CL_019</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Verify message status checkmark</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1. Observe sent message preview.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Checkmark should display (single=sent, double=delivered).</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>CL_020</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Verify long message truncation</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1. Send long message.
+2. Observe preview.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Long message should be truncated with ellipsis.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>CL_021</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Verify image/attachment preview</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1. Send image.
+2. Observe preview.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Preview should show attachment indicator (e.g., "📷 Photo").</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>CL_022</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>Verify preview updates on new message</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Receive new message.
 2. Observe preview.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Preview should update to show new message.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>CL_023</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Verify Preview Message</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>User is logged in with new conversation</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Verify empty preview for new conversation</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Start new conversation without messages.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>No preview or placeholder should display.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>CL_024</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Verify UI responsiveness</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Verify conversation list on desktop and mobile</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Test on desktop.
 2. Test on mobile.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>List should be functional on both platforms.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
@@ -1756,7 +1816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1885,77 +1945,87 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CL_035</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Security: Conversation List</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>User is not logged in</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify conversation list not accessible without authentication</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to access conversation list without logging in.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Should redirect to login page. No conversation data should be exposed.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>CL_035</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Security: Conversation List</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>User is not logged in</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Verify conversation list not accessible without authentication</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to access conversation list without logging in.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Should redirect to login page. No conversation data should be exposed.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>CL_036</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>User session expired</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify conversation list handles expired session</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. Let session expire.
 2. Try to interact with conversation list.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Should prompt re-authentication. No stale data should be accessible.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
@@ -1973,7 +2043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2194,74 +2264,84 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>CL_042</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Edge Case: Conversation List</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Verify conversation list when server returns error</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Simulate server error (500).
 2. Observe conversation list.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Error message should display with retry option. App should not crash.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>CL_043</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify conversation list with slow network (2G/3G)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Throttle network to 2G speed.
 2. Open conversation list.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Loading indicator should show. List should eventually load. No timeout crash.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>

--- a/Conversation_List/Conversation_List_Test_Cases.xlsx
+++ b/Conversation_List/Conversation_List_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -693,132 +693,175 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CL_008</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete Conversation</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and has conversations</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verify delete icon appears on swipe/hover</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. Swipe left on conversation (mobile) or hover (desktop).</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Delete icon (trash) should appear.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CL_007</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Verify User and Group Listing</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in with no conversations</t>
-        </is>
-      </c>
+          <t>CL_009</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Verify empty conversation list state</t>
+          <t>Verify delete confirmation dialog</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1. Login with new account.
-2. Navigate to Chats.</t>
+          <t>1. Click delete icon on conversation.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Empty state message should display.</t>
+          <t>Confirmation dialog should appear.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CL_010</t>
+        </is>
+      </c>
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and delete dialog shown</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Verify conversation deleted on confirm</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Click confirm in delete dialog.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Conversation should be removed from list.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CL_008</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete Conversation</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and has conversations</t>
-        </is>
-      </c>
+          <t>CL_011</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Verify delete icon appears on swipe/hover</t>
+          <t>Verify cancel delete keeps conversation</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1. Swipe left on conversation (mobile) or hover (desktop).</t>
+          <t>1. Click cancel in delete dialog.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Delete icon (trash) should appear.</t>
+          <t>Conversation should remain in list.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CL_009</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
+          <t>CL_013</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Verify Check Day</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and has conversations</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify delete confirmation dialog</t>
+          <t>Verify today's conversation shows time</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1. Click delete icon on conversation.</t>
+          <t>1. Observe conversation from today.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Confirmation dialog should appear.</t>
+          <t>Time should display (e.g., "02:35 AM").</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -830,29 +873,25 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CL_010</t>
+          <t>CL_014</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and delete dialog shown</t>
-        </is>
-      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify conversation deleted on confirm</t>
+          <t>Verify yesterday's conversation shows 'Yesterday'</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1. Click confirm in delete dialog.</t>
+          <t>1. Observe conversation from yesterday.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Conversation should be removed from list.</t>
+          <t>"Yesterday" should display instead of date.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -864,7 +903,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CL_011</t>
+          <t>CL_015</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -872,70 +911,90 @@
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify cancel delete keeps conversation</t>
+          <t>Verify older conversation shows date</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1. Click cancel in delete dialog.</t>
+          <t>1. Observe conversation older than yesterday.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Conversation should remain in list.</t>
+          <t>Date should display (e.g., "05/02/2026").</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>CL_016</t>
+        </is>
+      </c>
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Verify date updates after midnight</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1. Check conversation at 11:59 PM.
+2. Check again after midnight.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Date/time label should update appropriately.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CL_012</t>
+          <t>CL_017</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Verify Delete Conversation</t>
+          <t>Verify Preview Message</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, network disconnected</t>
+          <t>User is logged in and has conversations</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify delete fails without network</t>
+          <t>Verify last message preview displays</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1. Disconnect network.
-2. Try to delete conversation.</t>
+          <t>1. Observe conversation in list.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Error message should display.</t>
+          <t>Last message preview should display below name.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -945,49 +1004,58 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>CL_018</t>
+        </is>
+      </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Verify 'You:' prefix for sent messages</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1. Send message.
+2. Observe conversation preview.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Preview should show "You: [message]" for sent messages.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CL_013</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Verify Check Day</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and has conversations</t>
-        </is>
-      </c>
+          <t>CL_019</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify today's conversation shows time</t>
+          <t>Verify message status checkmark</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1. Observe conversation from today.</t>
+          <t>1. Observe sent message preview.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Time should display (e.g., "02:35 AM").</t>
+          <t>Checkmark should display (single=sent, double=delivered).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -999,7 +1067,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CL_014</t>
+          <t>CL_020</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
@@ -1007,29 +1075,30 @@
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify yesterday's conversation shows 'Yesterday'</t>
+          <t>Verify long message truncation</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1. Observe conversation from yesterday.</t>
+          <t>1. Send long message.
+2. Observe preview.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>"Yesterday" should display instead of date.</t>
+          <t>Long message should be truncated with ellipsis.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CL_015</t>
+          <t>CL_021</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
@@ -1037,29 +1106,30 @@
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify older conversation shows date</t>
+          <t>Verify image/attachment preview</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1. Observe conversation older than yesterday.</t>
+          <t>1. Send image.
+2. Observe preview.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Date should display (e.g., "05/02/2026").</t>
+          <t>Preview should show attachment indicator (e.g., "📷 Photo").</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CL_016</t>
+          <t>CL_022</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
@@ -1067,30 +1137,30 @@
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify date updates after midnight</t>
+          <t>Verify preview updates on new message</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1. Check conversation at 11:59 PM.
-2. Check again after midnight.</t>
+          <t>1. Receive new message.
+2. Observe preview.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Date/time label should update appropriately.</t>
+          <t>Preview should update to show new message.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CL_017</t>
+          <t>CL_024</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1100,291 +1170,171 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Verify Preview Message</t>
+          <t>Verify UI responsiveness</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and has conversations</t>
+          <t>User is logged in</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify last message preview displays</t>
+          <t>Verify conversation list on desktop and mobile</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1. Observe conversation in list.</t>
+          <t>1. Test on desktop.
+2. Test on mobile.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Last message preview should display below name.</t>
+          <t>List should be functional on both platforms.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CL_018</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Verify 'You:' prefix for sent messages</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1. Send message.
-2. Observe conversation preview.</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Preview should show "You: [message]" for sent messages.</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CL_019</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
+          <t>CL_007</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Verify User and Group Listing</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in with no conversations</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify message status checkmark</t>
+          <t>Verify empty conversation list state</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1. Observe sent message preview.</t>
+          <t>1. Login with new account.
+2. Navigate to Chats.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Checkmark should display (single=sent, double=delivered).</t>
+          <t>Empty state message should display.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CL_020</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
+          <t>CL_012</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete Conversation</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify long message truncation</t>
+          <t>Verify delete fails without network</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1. Send long message.
-2. Observe preview.</t>
+          <t>1. Disconnect network.
+2. Try to delete conversation.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Long message should be truncated with ellipsis.</t>
+          <t>Error message should display.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CL_021</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
+          <t>CL_023</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Verify Preview Message</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in with new conversation</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify image/attachment preview</t>
+          <t>Verify empty preview for new conversation</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1. Send image.
-2. Observe preview.</t>
+          <t>1. Start new conversation without messages.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Preview should show attachment indicator (e.g., "📷 Photo").</t>
+          <t>No preview or placeholder should display.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CL_022</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Verify preview updates on new message</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1. Receive new message.
-2. Observe preview.</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Preview should update to show new message.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CL_023</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Verify Preview Message</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in with new conversation</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Verify empty preview for new conversation</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1. Start new conversation without messages.</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>No preview or placeholder should display.</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
           <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CL_024</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Verify UI responsiveness</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Verify conversation list on desktop and mobile</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1. Test on desktop.
-2. Test on mobile.</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>List should be functional on both platforms.</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
         </is>
       </c>
     </row>

--- a/Conversation_List/Conversation_List_Test_Cases.xlsx
+++ b/Conversation_List/Conversation_List_Test_Cases.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +36,18 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +58,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,13 +85,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,898 +465,1573 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CL_001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Verify User and Group Listing</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and has conversations</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify conversation list displays users and groups</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Chats tab.
 2. Observe conversation list.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Both user chats and group chats should display in the list.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CL_002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify user conversation displays name and avatar</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Observe user conversation in list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>User name, profile picture, and last message should display.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CL_003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify group conversation displays name and avatar</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Observe group conversation in list.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Group name, group avatar/initials, and last message should display.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CL_004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify online status indicator</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Observe avatar in conversation list.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Online users/groups should show green dot indicator.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>CL_005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify conversations sorted by recent activity</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. Send message in older conversation.
 2. Observe list order.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Most recent conversation should move to top.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>CL_006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Verify clicking conversation opens chat</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. Click on any conversation.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Chat window should open with message history.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>CL_008</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Verify Delete Conversation</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>User is logged in and has conversations</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Verify delete icon appears on swipe/hover</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. Swipe left on conversation (mobile) or hover (desktop).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Delete icon (trash) should appear.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>CL_009</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Verify delete confirmation dialog</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. Click delete icon on conversation.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Confirmation dialog should appear.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>CL_010</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>User is logged in and delete dialog shown</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Verify conversation deleted on confirm</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. Click confirm in delete dialog.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Conversation should be removed from list.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>CL_011</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Verify cancel delete keeps conversation</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. Click cancel in delete dialog.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Conversation should remain in list.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>CL_013</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Verify Check Day</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>User is logged in and has conversations</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Verify today's conversation shows time</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. Observe conversation from today.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Time should display (e.g., "02:35 AM").</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>CL_014</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Verify yesterday's conversation shows 'Yesterday'</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. Observe conversation from yesterday.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>"Yesterday" should display instead of date.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>CL_015</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Verify older conversation shows date</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. Observe conversation older than yesterday.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Date should display (e.g., "05/02/2026").</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>CL_016</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Verify date updates after midnight</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. Check conversation at 11:59 PM.
 2. Check again after midnight.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Date/time label should update appropriately.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>CL_017</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Verify Preview Message</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>User is logged in and has conversations</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Verify last message preview displays</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. Observe conversation in list.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Last message preview should display below name.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>CL_018</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Verify 'You:' prefix for sent messages</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. Send message.
 2. Observe conversation preview.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Preview should show "You: [message]" for sent messages.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>CL_019</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Verify message status checkmark</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1. Observe sent message preview.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Checkmark should display (single=sent, double=delivered).</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>CL_020</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Verify long message truncation</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1. Send long message.
 2. Observe preview.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Long message should be truncated with ellipsis.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>CL_021</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Verify image/attachment preview</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>1. Send image.
 2. Observe preview.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Preview should show attachment indicator (e.g., "📷 Photo").</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>CL_022</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Verify preview updates on new message</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>1. Receive new message.
 2. Observe preview.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Preview should update to show new message.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>CL_024</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Verify UI responsiveness</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Verify conversation list on desktop and mobile</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>1. Test on desktop.
 2. Test on mobile.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>List should be functional on both platforms.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>CL_052</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Group Type Icons</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>hideGroupType=false, group conversations exist</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Verify group type icon shown for group conversations</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>1. Open conversation list
+2. Check group conversation items</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Group type icon (public/private/password) visible</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>CL_053</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Group Type Icons - Public</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Public group conversation</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Verify public group icon displayed</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>1. Check public group conversation</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Public group icon shown correctly</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>CL_054</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Group Type Icons - Private</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Private group conversation</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Verify private group icon displayed</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>1. Check private group conversation</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Private/lock group icon shown</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>CL_055</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Group Type Icons - Password</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Password protected group</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Verify password group icon displayed</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>1. Check password group conversation</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Password/shield group icon shown</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>CL_056</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Sound Notifications</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>disableSoundForMessages=false</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Verify sound plays on new message</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>1. Receive new message while in conversation list</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Incoming message sound plays</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>CL_057</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Custom Sound</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>customSoundForMessages set</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Verify custom sound plays for messages</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>1. Set custom sound URL
+2. Receive message</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Custom sound plays instead of default</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>CL_058</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Selection Mode - Single</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>selectionMode=single</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Verify single selection with radio buttons</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>1. Set selectionMode to single
+2. Click conversation</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Radio button shown, only one selectable</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>CL_059</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Selection Mode - Multiple</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>selectionMode=multiple</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Verify multiple selection with checkboxes</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>1. Set selectionMode to multiple
+2. Click conversations</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Checkboxes shown, multiple selectable</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>CL_060</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Context Menu - Delete</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>hideDeleteConversation=false</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Verify delete option in context menu</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>1. Right-click/long-press conversation
+2. Check menu</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Delete conversation option visible</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>CL_061</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Context Menu - Custom Options</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Custom options provided</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Verify custom options in context menu</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>1. Provide custom options via props
+2. Right-click conversation</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Custom options visible in context menu</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>CL_062</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Search Bar</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>showSearchBar=true</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Verify search bar appears in conversations</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>1. Set showSearchBar=true
+2. Check header</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Search bar visible in conversation list header</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>CL_063</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Typing Indicator in List</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>User typing in conversation</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Verify typing indicator in subtitle</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>1. Other user starts typing
+2. Check conversation subtitle</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Typing indicator shown in conversation subtitle</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>CL_007</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Verify User and Group Listing</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>User is logged in with no conversations</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Verify empty conversation list state</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>1. Login with new account.
 2. Navigate to Chats.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>Empty state message should display.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>CL_012</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Verify Delete Conversation</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>Verify delete fails without network</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to delete conversation.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>Error message should display.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>CL_023</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Verify Preview Message</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>User is logged in with new conversation</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>Verify empty preview for new conversation</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>1. Start new conversation without messages.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>No preview or placeholder should display.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>CL_064</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Group Type Hidden</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>hideGroupType=true</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Verify group type icon hidden</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>1. Set hideGroupType=true
+2. Check group conversations</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>No group type icons visible</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>CL_065</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Sound Disabled</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>disableSoundForMessages=true</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Verify no sound on new message</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>1. Disable sound
+2. Receive message</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>No sound plays</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>CL_066</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Delete Hidden</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>hideDeleteConversation=true</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Verify delete option hidden in context menu</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>1. Right-click conversation
+2. Check menu</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Delete option not visible</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>CL_067</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>User Status Hidden</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>hideUserStatus=true</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Verify online/offline indicator hidden</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>1. Set hideUserStatus=true
+2. Check user conversations</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>No online/offline status indicator</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1346,207 +2043,379 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0070AD47"/>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CL_025</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Integration: Conversation List with Message List</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in with conversations</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify opening conversation navigates to correct message list</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Click on a conversation.
 2. Verify messages belong to that conversation.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Message list should load messages only for the selected conversation. No cross-conversation data.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CL_026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify new message updates conversation list preview and order</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Send a message in an older conversation.
 2. Observe conversation list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Conversation should move to top with updated preview message and timestamp.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CL_027</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify read status syncs between conversation list and message list</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Open an unread conversation.
 2. Read messages.
 3. Go back to list.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Unread badge should disappear from the conversation in the list.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CL_028</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Integration: Conversation List with Notifications</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>User is logged in, app in background</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify notification updates conversation list on app resume</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Receive messages while app is in background.
 2. Open app.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Conversation list should refresh with new messages reflected in preview and order.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CL_068</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Delete + Message List</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Conversation deleted</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify message list clears after conversation delete</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Delete conversation
+2. Check message area</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Message list cleared, empty state shown</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CL_069</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Selection + Bulk Action</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Multiple conversations selected</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify bulk actions on selected conversations</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Select multiple conversations
+2. Perform bulk action</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Action applied to all selected conversations</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>CL_070</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Sound + Background</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>App in background</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify sound plays when app in background</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Put app in background
+2. Receive message</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Sound notification plays</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>CL_071</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Delete Last Conversation</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Only one conversation exists</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Verify deleting last conversation shows empty state</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. Delete the only conversation</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Empty state view displayed</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1558,199 +2427,330 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FFC000"/>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CL_029</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Regression: Conversation List after actions</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in with conversations</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify conversation list intact after deleting a conversation</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Delete a conversation.
 2. Observe remaining conversations.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Remaining conversations should maintain correct order, previews, and timestamps. No data corruption.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CL_030</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify conversation list intact after blocking a user</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Block a user.
 2. Observe conversation list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Blocked user's conversation should be handled per app policy (hidden or marked). Other conversations unaffected.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CL_031</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify conversation list after app update/restart</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Close and reopen the app.
 2. Observe conversation list.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>All conversations should reload correctly with accurate previews and order.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CL_032</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify conversation list after logout and re-login</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Logout.
 2. Login with same account.
 3. Observe conversation list.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>All previous conversations should load correctly.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CL_072</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Group Icon After Type Change</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Group type changed by admin</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify icon updates after group type change</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Admin changes group type
+2. Check conversation list</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Group type icon updated</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CL_073</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Sound After Toggle</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Sound toggled off then on</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify sound works after re-enabling</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Disable sound
+2. Re-enable
+3. Receive message</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Sound plays after re-enabling</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CL_074</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Selection After Refresh</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Selections made then list refreshed</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verify selections cleared after refresh</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. Select conversations
+2. Refresh list</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>All selections cleared</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1762,222 +2762,306 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FF0000"/>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CL_033</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Security: Conversation List</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify conversation list shows only authorized conversations</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Login as User A.
 2. Observe conversation list.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Only conversations where User A is a participant should display. No other users' conversations visible.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CL_034</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify conversation preview does not expose sensitive data</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Observe preview messages in conversation list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Sensitive content (passwords, tokens) should not be visible in preview. Media messages should show placeholder text.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CL_036</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>User session expired</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Verify conversation list handles expired session</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. Let session expire.
+2. Try to interact with conversation list.</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Should prompt re-authentication. No stale data should be accessible.</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CL_035</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Security: Conversation List</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>User is not logged in</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Verify conversation list not accessible without authentication</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to access conversation list without logging in.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Should redirect to login page. No conversation data should be exposed.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CL_075</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Delete Confirmation</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Delete option clicked</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify confirmation dialog before delete</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Click delete on conversation</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Confirmation dialog shown before deletion</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CL_036</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="n"/>
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>User session expired</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Verify conversation list handles expired session</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1. Let session expire.
-2. Try to interact with conversation list.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Should prompt re-authentication. No stale data should be accessible.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CL_035</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Security: Conversation List</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>User is not logged in</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify conversation list not accessible without authentication</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Try to access conversation list without logging in.</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Should redirect to login page. No conversation data should be exposed.</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>CL_076</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Delete Other User's Conversation</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Unauthorized delete attempt</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify cannot delete other user's conversations</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Attempt to delete via API manipulation</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Only own conversations deletable</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1993,307 +3077,424 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CL_037</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Edge Case: Conversation List</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify conversation list with 1000+ conversations</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Have an account with 1000+ conversations.
 2. Open conversation list.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>List should load with pagination/infinite scroll. No performance degradation or crash.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CL_038</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify conversation with extremely long group name</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Create a group with a 255-character name.
 2. Observe in conversation list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Group name should truncate with ellipsis. No layout breaking.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CL_039</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify conversation with special characters in name</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Have a conversation with user/group name containing emojis, unicode, RTL characters.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Name should display correctly without rendering issues.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CL_040</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify conversation list with rapid message updates</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Receive 50+ messages in quick succession across different conversations.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>List should update smoothly without flickering, freezing, or incorrect ordering.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>CL_041</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify conversation preview with empty message (media only)</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. Send an image with no caption in a conversation.
 2. Observe preview.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Preview should show placeholder like '📷 Photo' or 'Image' instead of blank.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CL_043</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify conversation list with slow network (2G/3G)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Throttle network to 2G speed.
+2. Open conversation list.</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Loading indicator should show. List should eventually load. No timeout crash.</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>CL_077</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>100+ Conversations</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>User has 100+ conversations</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify list handles large number of conversations</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Load conversation list with 100+ items</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>List loads with pagination/infinite scroll</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CL_078</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Rapid Selection Toggle</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Quick select/deselect</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verify rapid selection changes handled</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. Rapidly toggle selections</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>All selections tracked correctly</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>CL_042</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Edge Case: Conversation List</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Verify conversation list when server returns error</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. Simulate server error (500).
 2. Observe conversation list.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Error message should display with retry option. App should not crash.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CL_043</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Verify conversation list with slow network (2G/3G)</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1. Throttle network to 2G speed.
-2. Open conversation list.</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Loading indicator should show. List should eventually load. No timeout crash.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Medium / High</t>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CL_079</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Empty Conversation List</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>No conversations exist</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Verify empty state shown</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. New user with no conversations</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Empty state view displayed</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2309,193 +3510,278 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CL_044</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Boundary: Conversation List</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify conversation list with exactly 0 conversations</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Login with new account with no conversations.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Empty state should display correctly with appropriate message.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CL_045</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify conversation list with exactly 1 conversation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Have exactly 1 conversation.
 2. Open list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Single conversation should display correctly with all elements.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CL_046</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify preview message with 1 character</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Send a single character message.
 2. Observe preview.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Single character should display correctly in preview.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CL_047</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify preview message with maximum length text</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Send a very long message (5000+ chars).
 2. Observe preview.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Preview should truncate appropriately with ellipsis.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CL_080</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Conversation Limit 30</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Default limit of 30</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify 30 conversations loaded initially</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Open conversation list</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>30 conversations loaded, more on scroll</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>CL_081</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Conversation Limit 0</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>No conversations available</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify empty state with 0 conversations</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. User with no conversations</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Empty state displayed correctly</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2511,190 +3797,317 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CL_048</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Conversation Types</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify one-on-one conversation display</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Observe a one-on-one conversation in list.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Should show user avatar, name, last message preview, time, and unread count.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CL_049</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify public group conversation display</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Observe a public group conversation in list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Should show group avatar, group name, last message with sender prefix, time.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CL_050</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify private group conversation display</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Observe a private group conversation in list.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Should show group avatar with lock icon, group name, last message, time.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CL_051</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify password-protected group conversation display</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Observe a password-protected group conversation in list.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Should show group avatar, group name, last message, time. Password icon if applicable.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CL_082</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>User Conversation</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>1-on-1 chat conversation</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify user conversation display</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Check user conversation item</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>User avatar, name, last message shown</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CL_083</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Group Conversation</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Group chat conversation</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify group conversation display</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Check group conversation item</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Group avatar, name, last message, type icon shown</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CL_084</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Deleted User Conversation</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Conversation with deleted user</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verify handling of deleted user conversation</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. Check conversation with deleted user</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Conversation shown with appropriate fallback</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>

--- a/Conversation_List/Conversation_List_Test_Cases.xlsx
+++ b/Conversation_List/Conversation_List_Test_Cases.xlsx
@@ -67,7 +67,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -81,11 +81,12 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -98,6 +99,13 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -521,1517 +529,3024 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>CL_001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Verify User and Group Listing</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in and has conversations</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify conversation list displays users and groups</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Chats tab.
 2. Observe conversation list.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Both user chats and group chats should display in the list.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>CL_002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify user conversation displays name and avatar</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Observe user conversation in list.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>User name, profile picture, and last message should display.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>CL_003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify group conversation displays name and avatar</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Observe group conversation in list.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Group name, group avatar/initials, and last message should display.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>CL_004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify online status indicator</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Observe avatar in conversation list.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Online users/groups should show green dot indicator.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CL_005</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify conversations sorted by recent activity</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Send message in older conversation.
 2. Observe list order.</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Most recent conversation should move to top.</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>CL_006</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verify clicking conversation opens chat</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. Click on any conversation.</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Chat window should open with message history.</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>CL_008</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Verify Delete Conversation</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>User is logged in and has conversations</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Verify delete icon appears on swipe/hover</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>1. Swipe left on conversation (mobile) or hover (desktop).</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Delete icon (trash) should appear.</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>CL_009</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Verify delete confirmation dialog</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>1. Click delete icon on conversation.</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Confirmation dialog should appear.</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>CL_010</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>User is logged in and delete dialog shown</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Verify conversation deleted on confirm</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>1. Click confirm in delete dialog.</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Conversation should be removed from list.</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>CL_011</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Verify cancel delete keeps conversation</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>1. Click cancel in delete dialog.</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Conversation should remain in list.</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>CL_013</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Verify Check Day</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>User is logged in and has conversations</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Verify today's conversation shows time</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>1. Observe conversation from today.</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Time should display (e.g., "02:35 AM").</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>CL_014</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Verify yesterday's conversation shows 'Yesterday'</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>1. Observe conversation from yesterday.</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>"Yesterday" should display instead of date.</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>CL_015</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Verify older conversation shows date</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>1. Observe conversation older than yesterday.</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Date should display (e.g., "05/02/2026").</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>CL_016</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Verify date updates after midnight</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>1. Check conversation at 11:59 PM.
 2. Check again after midnight.</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Date/time label should update appropriately.</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>CL_017</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Verify Preview Message</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>User is logged in and has conversations</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Verify last message preview displays</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>1. Observe conversation in list.</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Last message preview should display below name.</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>CL_018</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Verify 'You:' prefix for sent messages</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>1. Send message.
 2. Observe conversation preview.</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Preview should show "You: [message]" for sent messages.</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>CL_019</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Verify message status checkmark</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>1. Observe sent message preview.</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Checkmark should display (single=sent, double=delivered).</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>CL_020</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Verify long message truncation</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>1. Send long message.
 2. Observe preview.</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Long message should be truncated with ellipsis.</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>CL_021</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Verify image/attachment preview</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>1. Send image.
 2. Observe preview.</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Preview should show attachment indicator (e.g., "📷 Photo").</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>CL_022</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Verify preview updates on new message</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>1. Receive new message.
 2. Observe preview.</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Preview should update to show new message.</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>CL_024</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Verify UI responsiveness</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Verify conversation list on desktop and mobile</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>1. Test on desktop.
 2. Test on mobile.</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>List should be functional on both platforms.</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>CL_052</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Group Type Icons</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>hideGroupType=false, group conversations exist</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Verify group type icon shown for group conversations</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>1. Open conversation list
 2. Check group conversation items</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Group type icon (public/private/password) visible</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>CL_053</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Group Type Icons - Public</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Public group conversation</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Verify public group icon displayed</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>1. Check public group conversation</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Public group icon shown correctly</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>CL_054</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Group Type Icons - Private</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Private group conversation</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Verify private group icon displayed</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>1. Check private group conversation</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Private/lock group icon shown</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>CL_055</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Group Type Icons - Password</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Password protected group</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Verify password group icon displayed</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>1. Check password group conversation</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Password/shield group icon shown</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>CL_056</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Sound Notifications</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>disableSoundForMessages=false</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Verify sound plays on new message</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>1. Receive new message while in conversation list</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Incoming message sound plays</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>CL_057</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Custom Sound</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>customSoundForMessages set</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Verify custom sound plays for messages</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>1. Set custom sound URL
 2. Receive message</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Custom sound plays instead of default</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>CL_058</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Selection Mode - Single</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>selectionMode=single</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Verify single selection with radio buttons</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>1. Set selectionMode to single
 2. Click conversation</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Radio button shown, only one selectable</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>CL_059</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Selection Mode - Multiple</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>selectionMode=multiple</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Verify multiple selection with checkboxes</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>1. Set selectionMode to multiple
 2. Click conversations</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Checkboxes shown, multiple selectable</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>CL_060</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Context Menu - Delete</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>hideDeleteConversation=false</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Verify delete option in context menu</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>1. Right-click/long-press conversation
 2. Check menu</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Delete conversation option visible</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>CL_061</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Context Menu - Custom Options</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Custom options provided</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Verify custom options in context menu</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>1. Provide custom options via props
 2. Right-click conversation</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Custom options visible in context menu</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>CL_062</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Search Bar</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>showSearchBar=true</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Verify search bar appears in conversations</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>1. Set showSearchBar=true
 2. Check header</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Search bar visible in conversation list header</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>CL_063</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Typing Indicator in List</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>User typing in conversation</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Verify typing indicator in subtitle</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>1. Other user starts typing
 2. Check conversation subtitle</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Typing indicator shown in conversation subtitle</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>CONV_001</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Home - Four Tabs Display</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>User logged in, home screen loaded</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Verify all 4 tabs are displayed</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1. Login and navigate to home
+2. Observe tab bar</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Chats, Calls, Users, Groups tabs should be visible with icons</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>CONV_002</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Home - Default Chats Tab</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Home screen loaded</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Verify Chats tab is active by default</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>1. Login to app
+2. Observe active tab</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Chats tab should be active/highlighted by default</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>CONV_003</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Home - Switch to Calls Tab</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Home screen loaded</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Verify switching to Calls tab</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>1. Click Calls tab
+2. Observe content change</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Call logs should be displayed, tab should be highlighted</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>CONV_004</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Home - Switch to Users Tab</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Home screen loaded</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Verify switching to Users tab</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>1. Click Users tab
+2. Observe content change</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Users list should be displayed, tab should be highlighted</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>CONV_005</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Home - Switch to Groups Tab</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Home screen loaded</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Verify switching to Groups tab</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>1. Click Groups tab
+2. Observe content change</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Groups list should be displayed with create group button, tab should be highlighted</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>CONV_006</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Home - Empty State for Chats</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>No conversation selected</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Verify empty state view when no chat is selected</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>1. Login to app
+2. Don't select any conversation</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Empty state view should be displayed in the messages area</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>CONV_007</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Home - Empty State for Calls</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Calls tab active, no call selected</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Verify empty state view for calls tab</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>1. Switch to Calls tab
+2. Don't select any call</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Calls-specific empty state view should be displayed</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>CONV_008</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Home - Tab Hover Effect</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Home screen loaded</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Verify tab hover visual feedback</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>1. Hover over each tab
+2. Observe visual change</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Tab icon and text should change to active style on hover</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>CONV_009</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Home - Theme Auto-Detection</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Home screen loaded</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Verify theme auto-detects OS preference</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>1. Set OS to dark mode
+2. Open app
+3. Observe theme</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>App should detect dark mode and apply dark theme via data-theme attribute</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>CONV_010</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Home - Theme Change Listener</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>App running</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Verify theme updates when OS preference changes</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>1. Open app in light mode
+2. Switch OS to dark mode
+3. Observe app</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>App should dynamically switch to dark theme without reload</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>CONV_011</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Context Menu - Display Options</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Chats tab active, logged in</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Verify context menu shows correct options</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>1. Click the menu icon in conversations header
+2. Observe options</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Should show: logged-in user name, Create Conversation, Log Out</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>CONV_012</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Context Menu - Logged In User Info</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>User logged in</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Verify logged-in user name displayed in menu</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1. Open context menu
+2. Observe first option</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>First option should show the logged-in user's name with user icon</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>CONV_013</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Context Menu - Create Conversation</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Context menu open</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Verify Create Conversation opens new chat view</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>1. Click 'Create Conversation' option
+2. Observe view change</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>New Chat view should open with User/Group tabs</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>CONV_014</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Logout - Successful Logout</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>User logged in</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Verify logout functionality</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1. Open context menu
+2. Click 'Log Out'
+3. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>CometChatUIKit.logout() called, navigate to /login, app state reset</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>CONV_015</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>New Chat - User Tab Default</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>New Chat view opened</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Verify User tab is default in new chat</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>1. Open new chat view
+2. Observe default tab</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>User tab should be active by default, users list displayed</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>CONV_016</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>New Chat - Switch to Group Tab</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>New Chat view opened</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Verify switching to Group tab</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>1. Open new chat view
+2. Click Group tab</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Group tab should activate, joined groups list displayed</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>CONV_017</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>New Chat - Select User</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>New Chat view, User tab active</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Verify selecting a user starts conversation</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. Click on a user from the list
+2. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>New chat should open with selected user, new chat view closes</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>CONV_018</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>New Chat - Select Joined Group</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>New Chat view, Group tab active</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Verify selecting a joined group opens chat</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>1. Click on a joined group
+2. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Chat should open with selected group, new chat view closes</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>CONV_019</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>New Chat - Back Button</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>New Chat view opened</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Verify back button closes new chat view</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. Click back button in new chat header
+2. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>New chat view should close, return to previous state</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>CONV_020</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>New Chat - Auto-Join Public Group</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>New Chat view, Group tab, unjoined public group</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Verify auto-join for public groups</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1. Click on an unjoined public group
+2. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Should auto-join the group via CometChat.joinGroup() and open chat</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>CONV_021</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>New Chat - Password Group Join Dialog</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>New Chat view, Group tab, password-protected group</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Verify password dialog for protected groups</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1. Click on a password-protected unjoined group
+2. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Join Group password dialog should appear</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>CONV_022</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Toast - Block User Toast</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>User blocked</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Verify toast on user block</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>1. Block a user
+2. Observe toast</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Toast should show 'Blocked successfully'</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>CONV_023</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Toast - Ownership Transfer Toast</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Ownership transferred</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Verify toast on ownership transfer</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1. Transfer ownership
+2. Observe toast</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Toast should show 'Ownership transferred successfully'</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>CONV_024</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Toast - Scope Change Toast</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Member scope changed</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Verify toast on scope change</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>1. Change member scope
+2. Observe toast</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Toast should show 'Permissions updated successfully'</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>CONV_025</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Toast - Member Added Toast</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Member added to group</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Verify toast on member add</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>1. Add member to group
+2. Observe toast</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Toast should show 'Member added'</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>CONV_026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Toast - Member Banned Toast</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Member banned</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Verify toast on member ban</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>1. Ban a member
+2. Observe toast</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Toast should show 'Member banned'</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>CONV_027</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Toast - Member Unbanned Toast</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Member unbanned</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Verify toast on member unban</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>1. Unban a member
+2. Observe toast</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Toast should show 'Member unbanned'</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>CONV_028</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Toast - Member Kicked Toast</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Member kicked</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Verify toast on member kick</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>1. Kick a member
+2. Observe toast</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Toast should show 'Member removed'</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>CONV_029</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Toast - Leave Group Toast</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>User left group</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Verify toast on leaving group</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>1. Leave a group
+2. Observe toast</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Toast should show 'Group left'</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>CONV_030</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Toast - Delete &amp; Exit Toast</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Group deleted</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Verify toast on delete &amp; exit</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>1. Delete &amp; exit group
+2. Observe toast</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Toast should show 'Group left and chat deleted'</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>CONV_031</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Toast - Delete Chat Toast</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Chat deleted</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Verify toast on chat deletion</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>1. Delete a chat
+2. Observe toast</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Toast should show 'Chat deleted successfully'</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>CONV_032</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Toast - Close Toast</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Toast displayed</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Verify toast can be closed</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>1. Trigger any toast
+2. Click close on toast</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Toast should disappear</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>CL_007</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Verify User and Group Listing</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>User is logged in with no conversations</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Verify empty conversation list state</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Login with new account.
 2. Navigate to Chats.</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>Empty state message should display.</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>CL_012</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Verify Delete Conversation</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Verify delete fails without network</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to delete conversation.</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>Error message should display.</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>CL_023</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Verify Preview Message</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>User is logged in with new conversation</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Verify empty preview for new conversation</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Start new conversation without messages.</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>No preview or placeholder should display.</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>CL_064</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Group Type Hidden</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>hideGroupType=true</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Verify group type icon hidden</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Set hideGroupType=true
 2. Check group conversations</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>No group type icons visible</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>CL_065</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Sound Disabled</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>disableSoundForMessages=true</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Verify no sound on new message</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Disable sound
 2. Receive message</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>No sound plays</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>CL_066</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>Delete Hidden</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>hideDeleteConversation=true</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Verify delete option hidden in context menu</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Right-click conversation
 2. Check menu</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>Delete option not visible</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>CL_067</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>User Status Hidden</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>hideUserStatus=true</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Verify online/offline indicator hidden</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Set hideUserStatus=true
 2. Check user conversations</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>No online/offline status indicator</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>CONV_033</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Home - No Credentials Redirect</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>No credentials available</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Verify redirect when credentials missing</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>1. Clear localStorage and AppConstants
+2. Navigate to /home</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Should redirect to /credentials screen</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>CONV_034</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Home - Not Logged In Redirect</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Credentials exist but user not logged in</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Verify redirect when not logged in</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>1. Have credentials but no active session
+2. Navigate to /home</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Should redirect to /login screen</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>CONV_035</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Logout - Logout Failure</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>User logged in, network error</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Verify logout error handling</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>1. Disconnect network
+2. Attempt logout</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Error should be caught and logged, app should handle gracefully</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2047,7 +3562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2103,317 +3618,490 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>CL_025</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Integration: Conversation List with Message List</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in with conversations</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify opening conversation navigates to correct message list</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Click on a conversation.
 2. Verify messages belong to that conversation.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Message list should load messages only for the selected conversation. No cross-conversation data.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>CL_026</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify new message updates conversation list preview and order</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Send a message in an older conversation.
 2. Observe conversation list.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Conversation should move to top with updated preview message and timestamp.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>CL_027</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify read status syncs between conversation list and message list</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Open an unread conversation.
 2. Read messages.
 3. Go back to list.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Unread badge should disappear from the conversation in the list.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>CL_028</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Integration: Conversation List with Notifications</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>User is logged in, app in background</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify notification updates conversation list on app resume</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Receive messages while app is in background.
 2. Open app.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Conversation list should refresh with new messages reflected in preview and order.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CL_068</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Delete + Message List</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Conversation deleted</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify message list clears after conversation delete</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Delete conversation
 2. Check message area</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Message list cleared, empty state shown</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>CL_069</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Selection + Bulk Action</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Multiple conversations selected</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verify bulk actions on selected conversations</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. Select multiple conversations
 2. Perform bulk action</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Action applied to all selected conversations</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>CL_070</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Sound + Background</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>App in background</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Verify sound plays when app in background</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>1. Put app in background
 2. Receive message</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Sound notification plays</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>CONV_036</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Home - Tab Switch Resets Side Panel</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Side panel open</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Verify switching tabs closes side panel</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. Open user/group details side panel
+2. Switch to different tab</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Side panel should close, threaded message and search should reset</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>CONV_037</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Home - Incoming Call Component</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>User logged in</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Verify CometChatIncomingCall component is rendered</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>1. Login to app
+2. Inspect home screen components</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>CometChatIncomingCall component should be present for receiving calls</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CONV_038</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Logout - State Reset Integration</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>User logged in with active conversations</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify all state is reset on logout</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Open conversations, select items
+2. Logout
+3. Login again</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>All selectedItem, newChat, sideComponent states should be reset to defaults</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CONV_039</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>New Chat - Groups Joined Only Filter</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>New Chat view, Group tab</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify groups list shows only joined groups</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Open new chat
+2. Switch to Group tab
+3. Observe list</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>GroupsRequestBuilder should use joinedOnly(true) with limit 30</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>CL_071</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Delete Last Conversation</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Only one conversation exists</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Verify deleting last conversation shows empty state</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Delete the only conversation</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Empty state view displayed</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2428,6 +4116,438 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>CL_029</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Regression: Conversation List after actions</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>User is logged in with conversations</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify conversation list intact after deleting a conversation</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Delete a conversation.
+2. Observe remaining conversations.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Remaining conversations should maintain correct order, previews, and timestamps. No data corruption.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>CL_030</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify conversation list intact after blocking a user</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Block a user.
+2. Observe conversation list.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Blocked user's conversation should be handled per app policy (hidden or marked). Other conversations unaffected.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>CL_031</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify conversation list after app update/restart</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Close and reopen the app.
+2. Observe conversation list.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>All conversations should reload correctly with accurate previews and order.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>CL_032</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify conversation list after logout and re-login</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Logout.
+2. Login with same account.
+3. Observe conversation list.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>All previous conversations should load correctly.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>CL_072</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Group Icon After Type Change</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Group type changed by admin</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verify icon updates after group type change</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1. Admin changes group type
+2. Check conversation list</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Group type icon updated</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>CL_073</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Sound After Toggle</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Sound toggled off then on</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify sound works after re-enabling</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Disable sound
+2. Re-enable
+3. Receive message</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Sound plays after re-enabling</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CONV_040</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Home - State Persistence Across Tabs</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Conversation selected in Chats tab</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verify selected item persists when switching back</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. Select a conversation in Chats
+2. Switch to Users tab
+3. Switch back to Chats</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Previously selected conversation should still be active</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>CONV_041</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>New Chat - Side Panel Closes</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Side panel open, new chat opened</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Verify side panel closes when new chat opens</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. Open user details side panel
+2. Click Create Conversation
+3. Observe</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Side panel should close when new chat view opens</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CL_074</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Selection After Refresh</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Selections made then list refreshed</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify selections cleared after refresh</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Select conversations
+2. Refresh list</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>All selections cleared</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2487,270 +4607,289 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>CL_029</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Regression: Conversation List after actions</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>User is logged in with conversations</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify conversation list intact after deleting a conversation</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Delete a conversation.
-2. Observe remaining conversations.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Remaining conversations should maintain correct order, previews, and timestamps. No data corruption.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>CL_033</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Security: Conversation List</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify conversation list shows only authorized conversations</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Login as User A.
+2. Observe conversation list.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Only conversations where User A is a participant should display. No other users' conversations visible.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>CL_030</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify conversation list intact after blocking a user</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Block a user.
-2. Observe conversation list.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Blocked user's conversation should be handled per app policy (hidden or marked). Other conversations unaffected.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>CL_034</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify conversation preview does not expose sensitive data</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Observe preview messages in conversation list.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Sensitive content (passwords, tokens) should not be visible in preview. Media messages should show placeholder text.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>CL_031</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify conversation list after app update/restart</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Close and reopen the app.
-2. Observe conversation list.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>All conversations should reload correctly with accurate previews and order.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>CL_036</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>User session expired</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify conversation list handles expired session</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Let session expire.
+2. Try to interact with conversation list.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Should prompt re-authentication. No stale data should be accessible.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>CL_032</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify conversation list after logout and re-login</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Logout.
-2. Login with same account.
-3. Observe conversation list.</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>All previous conversations should load correctly.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>CL_075</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Delete Confirmation</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Delete option clicked</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify confirmation dialog before delete</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Click delete on conversation</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Confirmation dialog shown before deletion</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>CL_072</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Group Icon After Type Change</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Group type changed by admin</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Verify icon updates after group type change</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. Admin changes group type
-2. Check conversation list</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Group type icon updated</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CL_073</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Sound After Toggle</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Sound toggled off then on</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verify sound works after re-enabling</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. Disable sound
-2. Re-enable
-3. Receive message</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Sound plays after re-enabling</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>CL_035</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Security: Conversation List</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>User is not logged in</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify conversation list not accessible without authentication</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Try to access conversation list without logging in.</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Should redirect to login page. No conversation data should be exposed.</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>CL_076</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Delete Other User's Conversation</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Unauthorized delete attempt</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Verify cannot delete other user's conversations</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>1. Attempt to delete via API manipulation</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Only own conversations deletable</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>CL_074</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>CONV_042</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Selection After Refresh</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Selections made then list refreshed</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Verify selections cleared after refresh</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. Select conversations
-2. Refresh list</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>All selections cleared</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Home - Unauthorized Access</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>User not authenticated</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Verify home screen cannot be accessed without login</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. Clear session
+2. Directly navigate to /home URL</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Should redirect to login/credentials, not show home content</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2759,14 +4898,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00C00000"/>
+    <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2822,246 +4961,507 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>CL_033</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Security: Conversation List</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>CL_037</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Edge Case: Conversation List</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify conversation list shows only authorized conversations</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Login as User A.
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify conversation list with 1000+ conversations</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Have an account with 1000+ conversations.
+2. Open conversation list.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>List should load with pagination/infinite scroll. No performance degradation or crash.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>CL_038</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify conversation with extremely long group name</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Create a group with a 255-character name.
+2. Observe in conversation list.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Group name should truncate with ellipsis. No layout breaking.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>CL_039</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify conversation with special characters in name</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Have a conversation with user/group name containing emojis, unicode, RTL characters.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Name should display correctly without rendering issues.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>CL_040</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify conversation list with rapid message updates</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Receive 50+ messages in quick succession across different conversations.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>List should update smoothly without flickering, freezing, or incorrect ordering.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>CL_041</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verify conversation preview with empty message (media only)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1. Send an image with no caption in a conversation.
+2. Observe preview.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Preview should show placeholder like '📷 Photo' or 'Image' instead of blank.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>CL_043</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify conversation list with slow network (2G/3G)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Throttle network to 2G speed.
+2. Open conversation list.</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Loading indicator should show. List should eventually load. No timeout crash.</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>CL_077</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>100+ Conversations</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>User has 100+ conversations</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Verify list handles large number of conversations</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>1. Load conversation list with 100+ items</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>List loads with pagination/infinite scroll</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>CL_078</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Rapid Selection Toggle</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Quick select/deselect</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Verify rapid selection changes handled</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. Rapidly toggle selections</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>All selections tracked correctly</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CONV_043</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Home - Mobile Breakpoint (768px)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Browser window resizable</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Verify mobile layout at 768px breakpoint</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Resize browser to 768px width
+2. Observe layout changes</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Layout should switch to mobile view with back button on messages</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>CONV_044</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Home - Resize Window Dynamically</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>App running in browser</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Verify responsive behavior on window resize</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>1. Start at desktop width
+2. Gradually resize to mobile
+3. Resize back to desktop</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Layout should adapt dynamically at 768px breakpoint</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>CONV_045</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>New Chat - Click Own User</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>New Chat view, User tab</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Verify behavior when clicking own user in list</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>1. Find logged-in user in users list
+2. Click on it</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Should not open chat with self (openChatForUser checks uid === loggedInUser)</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>CL_042</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case: Conversation List</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Verify conversation list when server returns error</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1. Simulate server error (500).
 2. Observe conversation list.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Only conversations where User A is a participant should display. No other users' conversations visible.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>CL_034</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify conversation preview does not expose sensitive data</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Observe preview messages in conversation list.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Sensitive content (passwords, tokens) should not be visible in preview. Media messages should show placeholder text.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>CL_036</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>User session expired</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify conversation list handles expired session</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Let session expire.
-2. Try to interact with conversation list.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Should prompt re-authentication. No stale data should be accessible.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>CL_075</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Delete Confirmation</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Delete option clicked</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify confirmation dialog before delete</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Click delete on conversation</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Confirmation dialog shown before deletion</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CL_035</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display with retry option. App should not crash.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>CL_079</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Security: Conversation List</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>User is not logged in</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verify conversation list not accessible without authentication</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. Try to access conversation list without logging in.</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Should redirect to login page. No conversation data should be exposed.</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>CL_076</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Delete Other User's Conversation</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Unauthorized delete attempt</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Verify cannot delete other user's conversations</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. Attempt to delete via API manipulation</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Only own conversations deletable</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Empty Conversation List</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>No conversations exist</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty state shown</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1. New user with no conversations</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Empty state view displayed</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -3070,14 +5470,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00ED7D31"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3133,368 +5533,350 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>CL_037</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Edge Case: Conversation List</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>CL_044</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Boundary: Conversation List</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify conversation list with 1000+ conversations</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Have an account with 1000+ conversations.
-2. Open conversation list.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>List should load with pagination/infinite scroll. No performance degradation or crash.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify conversation list with exactly 0 conversations</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Login with new account with no conversations.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Empty state should display correctly with appropriate message.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>CL_038</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify conversation with extremely long group name</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Create a group with a 255-character name.
-2. Observe in conversation list.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Group name should truncate with ellipsis. No layout breaking.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>CL_045</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify conversation list with exactly 1 conversation</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Have exactly 1 conversation.
+2. Open list.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Single conversation should display correctly with all elements.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>CL_039</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify conversation with special characters in name</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Have a conversation with user/group name containing emojis, unicode, RTL characters.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Name should display correctly without rendering issues.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>CL_046</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify preview message with 1 character</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Send a single character message.
+2. Observe preview.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Single character should display correctly in preview.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>CL_047</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify preview message with maximum length text</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Send a very long message (5000+ chars).
+2. Observe preview.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Preview should truncate appropriately with ellipsis.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>CL_040</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify conversation list with rapid message updates</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Receive 50+ messages in quick succession across different conversations.</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>List should update smoothly without flickering, freezing, or incorrect ordering.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>CL_041</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Verify conversation preview with empty message (media only)</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. Send an image with no caption in a conversation.
-2. Observe preview.</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Preview should show placeholder like '📷 Photo' or 'Image' instead of blank.</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>CL_080</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Conversation Limit 30</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Default limit of 30</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verify 30 conversations loaded initially</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1. Open conversation list</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>30 conversations loaded, more on scroll</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CL_043</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verify conversation list with slow network (2G/3G)</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. Throttle network to 2G speed.
-2. Open conversation list.</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Loading indicator should show. List should eventually load. No timeout crash.</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Medium / High</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CONV_046</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Home - Exactly 768px Width</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Browser window at 768px</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Verify behavior at exact breakpoint</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1. Set window width to exactly 768px
+2. Observe layout</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Should be at the boundary of mobile/desktop layout</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>CL_077</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>100+ Conversations</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>User has 100+ conversations</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Verify list handles large number of conversations</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. Load conversation list with 100+ items</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>List loads with pagination/infinite scroll</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>CONV_047</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Home - 769px Width</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Browser window at 769px</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Verify desktop layout at 769px</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>1. Set window width to 769px
+2. Observe layout</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Should show desktop layout without back button</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>CL_078</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Rapid Selection Toggle</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Quick select/deselect</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Verify rapid selection changes handled</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. Rapidly toggle selections</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>All selections tracked correctly</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>CONV_048</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Home - 767px Width</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Browser window at 767px</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Verify mobile layout at 767px</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. Set window width to 767px
+2. Observe layout</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Should show mobile layout with back button on messages</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>CL_042</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CL_081</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Edge Case: Conversation List</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Verify conversation list when server returns error</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. Simulate server error (500).
-2. Observe conversation list.</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Error message should display with retry option. App should not crash.</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>CL_079</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Empty Conversation List</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>No conversations exist</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Verify empty state shown</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. New user with no conversations</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Empty state view displayed</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Conversation Limit 0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>No conversations available</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty state with 0 conversations</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. User with no conversations</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Empty state displayed correctly</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3503,14 +5885,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007030A0"/>
+    <tabColor rgb="0000B0F0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3566,546 +5948,354 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>CL_044</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Boundary: Conversation List</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>CL_048</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning: Conversation Types</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify conversation list with exactly 0 conversations</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Login with new account with no conversations.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Empty state should display correctly with appropriate message.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify one-on-one conversation display</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Observe a one-on-one conversation in list.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Should show user avatar, name, last message preview, time, and unread count.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>CL_049</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify public group conversation display</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Observe a public group conversation in list.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Should show group avatar, group name, last message with sender prefix, time.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>CL_050</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify private group conversation display</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Observe a private group conversation in list.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Should show group avatar with lock icon, group name, last message, time.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>CL_051</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify password-protected group conversation display</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Observe a password-protected group conversation in list.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Should show group avatar, group name, last message, time. Password icon if applicable.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>CL_045</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify conversation list with exactly 1 conversation</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Have exactly 1 conversation.
-2. Open list.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Single conversation should display correctly with all elements.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>CL_046</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify preview message with 1 character</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Send a single character message.
-2. Observe preview.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Single character should display correctly in preview.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>CL_047</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify preview message with maximum length text</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Send a very long message (5000+ chars).
-2. Observe preview.</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Preview should truncate appropriately with ellipsis.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>CL_080</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Conversation Limit 30</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Default limit of 30</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Verify 30 conversations loaded initially</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. Open conversation list</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>30 conversations loaded, more on scroll</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>CL_082</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>User Conversation</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>1-on-1 chat conversation</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verify user conversation display</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1. Check user conversation item</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>User avatar, name, last message shown</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>CL_083</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Group Conversation</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Group chat conversation</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify group conversation display</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Check group conversation item</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Group avatar, name, last message, type icon shown</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CONV_049</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Home - Desktop Width (&gt;768px)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Browser at desktop width</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verify desktop layout class</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. Open app at 1024px width
+2. Observe layout</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Three-panel layout: selector, messages, side component</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>CL_081</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>CONV_050</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Home - Mobile Width (&lt;768px)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Browser at mobile width</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Verify mobile layout class</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. Open app at 375px width
+2. Observe layout</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Single panel with navigation, back button visible</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CL_084</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Conversation Limit 0</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>No conversations available</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Verify empty state with 0 conversations</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. User with no conversations</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Empty state displayed correctly</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0000B0F0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Priority/Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>CL_048</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning: Conversation Types</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify one-on-one conversation display</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Observe a one-on-one conversation in list.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Should show user avatar, name, last message preview, time, and unread count.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>CL_049</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify public group conversation display</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Observe a public group conversation in list.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Should show group avatar, group name, last message with sender prefix, time.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>CL_050</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify private group conversation display</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Observe a private group conversation in list.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Should show group avatar with lock icon, group name, last message, time.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>CL_051</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify password-protected group conversation display</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Observe a password-protected group conversation in list.</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Should show group avatar, group name, last message, time. Password icon if applicable.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>CL_082</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>User Conversation</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>1-on-1 chat conversation</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Verify user conversation display</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. Check user conversation item</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>User avatar, name, last message shown</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CL_083</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Group Conversation</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Group chat conversation</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verify group conversation display</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. Check group conversation item</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Group avatar, name, last message, type icon shown</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>CL_084</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Deleted User Conversation</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Conversation with deleted user</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Verify handling of deleted user conversation</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>1. Check conversation with deleted user</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Conversation shown with appropriate fallback</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
